--- a/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,405 +656,418 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E7" s="2">
         <v>45137</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44955</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44864</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44682</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44591</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44409</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44318</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44129</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44038</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43947</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43856</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43765</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43674</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43583</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43492</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43401</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43310</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43219</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43128</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43037</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42946</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42764</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>200900</v>
+      </c>
+      <c r="E8" s="3">
         <v>238400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>236500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>167500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>177600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>209300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>202100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>190600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>194900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>185000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>170400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>164700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>154100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>143700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>132700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>138000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>141000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>137100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>131400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>160000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>173600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>163200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>130400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>140600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>150300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>153100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>143800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>140000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>137200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E9" s="3">
         <v>137300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>133100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>70300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>61900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>74500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>72900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>73400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>71200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>69600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>65500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>64200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>60000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>55400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>51900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>53700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>54800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>52300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>50100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>61100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>67000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>63100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>59000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>55200</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>60900</v>
       </c>
       <c r="AB9" s="3">
         <v>60900</v>
       </c>
       <c r="AC9" s="3">
+        <v>60900</v>
+      </c>
+      <c r="AD9" s="3">
         <v>58900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>56500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E10" s="3">
         <v>101100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>103400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>97200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>115700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>134800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>129200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>117200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>123700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>115400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>104900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>100500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>94100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>88300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>80800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>84300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>86200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>84800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>81300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>98900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>106600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>100100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>71400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>85400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>89400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>92200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>84900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>83500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,97 +1099,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E12" s="3">
         <v>47400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>50600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>52500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>35100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>40600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>38800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>38300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>37300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>35500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>36800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>32800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>29200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>27600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>28000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>27000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>25900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>27200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>27600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>27100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>28100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>26200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>23800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>27600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>27400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>26000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>25400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1264,97 +1281,103 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E14" s="3">
         <v>289500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>11100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>9300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-18400</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1300</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>2000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>30100</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5900</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-25000</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1364,23 +1387,23 @@
       <c r="E15" s="3">
         <v>4900</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1000</v>
       </c>
       <c r="H15" s="3">
         <v>1000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>1000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1300</v>
       </c>
       <c r="L15" s="3">
         <v>1300</v>
@@ -1389,52 +1412,52 @@
         <v>1300</v>
       </c>
       <c r="N15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O15" s="3">
         <v>1600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>5100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>6700</v>
-      </c>
-      <c r="W15" s="3">
-        <v>6500</v>
       </c>
       <c r="X15" s="3">
         <v>6500</v>
       </c>
       <c r="Y15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="Z15" s="3">
         <v>7000</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>7500</v>
       </c>
       <c r="AA15" s="3">
         <v>7500</v>
       </c>
       <c r="AB15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AC15" s="3">
         <v>6700</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>6300</v>
       </c>
       <c r="AD15" s="3">
         <v>6300</v>
@@ -1442,8 +1465,11 @@
       <c r="AE15" s="3">
         <v>6300</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1498,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>215300</v>
+      </c>
+      <c r="E17" s="3">
         <v>538700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>248500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>224700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>147500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>144800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>155100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>148000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>157700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>148800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>142600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>147000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>132900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>126400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>120600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>137700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>123100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>125400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>119200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>126200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>161700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>130300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>133500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>126600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>132700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>134200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>125500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>124700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>98100</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-300300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-57200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>30100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>64500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>47000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>42600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>37200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>36200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>27800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>33800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>32900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>14000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>17600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>18900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>18300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>15300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>39100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1683,212 +1716,219 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E20" s="3">
         <v>1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-276700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-41800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>38200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>72100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>54800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>49900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>44800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>44200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>35200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>25400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>28800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>24800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>9600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>28300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>26500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>48000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>25800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>45600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>25900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>31500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>30500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>28900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>26000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>50000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E22" s="3">
         <v>26600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1200</v>
       </c>
       <c r="L22" s="3">
         <v>1200</v>
@@ -1897,46 +1937,46 @@
         <v>1200</v>
       </c>
       <c r="N22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O22" s="3">
         <v>1500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2400</v>
-      </c>
-      <c r="X22" s="3">
-        <v>2200</v>
       </c>
       <c r="Y22" s="3">
         <v>2200</v>
       </c>
       <c r="Z22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AA22" s="3">
         <v>1900</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>2000</v>
       </c>
       <c r="AB22" s="3">
         <v>2000</v>
@@ -1945,191 +1985,200 @@
         <v>2000</v>
       </c>
       <c r="AD22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>3400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-325400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-31800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-60100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>29100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>63300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>46100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>41200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>36100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>35200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>26600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>16200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>19900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>16300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>33200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>31300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>10800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>16800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>16700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>15600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>11000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>36500</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>56600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-9100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>3000</v>
       </c>
       <c r="L24" s="3">
         <v>3000</v>
       </c>
       <c r="M24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N24" s="3">
         <v>3200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-17500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-52200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2217,186 +2266,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-382000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-29400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-51000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>51300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>38000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>34800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>33100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>32300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>13600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>13200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>26600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>25200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>63100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>13500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>12600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>11800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>8000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-382000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-29400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-51000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>22700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>51600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>38000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>34800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>34400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>32900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>15700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>14000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>26500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>7500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>25200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>12400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>63000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>13300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>11800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>8000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2484,8 +2542,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2525,8 +2586,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>24</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>24</v>
@@ -2543,23 +2604,23 @@
       <c r="U29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="W29" s="3">
         <v>-6600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>4700</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-64300</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -2573,8 +2634,11 @@
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2726,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,186 +2818,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-382000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-29400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-51000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>22700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>51600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>38000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>34800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>34400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>32900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>23500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>15700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>14000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>12200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>25200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>12400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>13300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>11800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>8000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3094,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-382000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-29400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-51000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>22700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>51600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>38000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>34800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>34400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>32900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>23500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>15700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>14000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>12200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>25200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>12400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>13300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>11800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>8000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E38" s="2">
         <v>45137</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44955</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44864</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44682</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44591</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44409</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44318</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44129</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44038</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43947</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43856</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43765</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43674</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43583</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43492</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43401</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43310</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43219</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43128</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43037</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42946</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42764</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3319,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,97 +3353,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>123800</v>
+      </c>
+      <c r="E41" s="3">
         <v>147900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>164200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>235500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>617800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>362200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>275200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>279600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>276600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>262700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>258200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>268900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>262300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>281500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>268900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>293300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>283100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>287800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>287300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>312100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>312200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>311300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>303300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>307900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>291100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>277900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>281600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>297100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>297900</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3445,364 +3535,379 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E43" s="3">
         <v>159100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>145400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>161700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>80500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>71100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>66400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>71500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>74300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>73100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>66500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>70400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>58700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>51700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>49500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>61900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>61400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>58600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>66500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>79200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>83800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>78400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>65600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>53200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>66500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>61200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>55900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>51400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>160600</v>
+      </c>
+      <c r="E44" s="3">
         <v>180200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>213200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>207700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>111100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>107600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>106900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>114000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>105200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>103000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>93900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>87500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>78400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>77500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>76900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>73000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>70100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>75100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>73500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>63700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>61200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>58900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>65500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>71100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>71200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>75000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>76800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>65900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>62700</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>131400</v>
+      </c>
+      <c r="E45" s="3">
         <v>142700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>141600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>117900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>36200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>47000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>37200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>46100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>47900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>48400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>43200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>37000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>32500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>25400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>31700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>29800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>30300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>29200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>29700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>33000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>29100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>21000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>24800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>21500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>24000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>572400</v>
+      </c>
+      <c r="E46" s="3">
         <v>629900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>664400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>722800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>835200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>577100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>495400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>502300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>496400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>484800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>461400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>474700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>447700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>453900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>432300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>460700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>440000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>453300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>457000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>485300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>486400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>478300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>467400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>461200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>449800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>438800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>435700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>438400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3881,195 +3986,204 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>24</v>
+      <c r="AC47" s="3">
+        <v>0</v>
       </c>
       <c r="AD47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF47" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>158800</v>
+      </c>
+      <c r="E48" s="3">
         <v>192200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>195200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>201100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>153700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>153500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>152700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>154700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>151400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>153700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>146600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>147300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>139600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>142700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>141700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>135400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>134200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>136700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>138200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>118500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>119500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>122600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>122500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>124600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>123400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>118700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>110300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>108900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>95500</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1181900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1200800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1487600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1496800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>354000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>355000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>356100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>357900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>359000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>360300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>361600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>362900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>364500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>366300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>368300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>371200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>374900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>378600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>382600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>387700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>395500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>393500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>395100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>402100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>409600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>421700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>385200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>391500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>397800</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4271,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,97 +4363,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E52" s="3">
         <v>95600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>152800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>148900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>123900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>114300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>111700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>116000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>114500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>101200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>100100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>97200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>96100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>91100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>81000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>85200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>90100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>87700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>75700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>71300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>83000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>114400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>113800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>97900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>88200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>82100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>76100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>72700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4547,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2038100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2118600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2500000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2569600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1466900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1199800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1115900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1130900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1121300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1100000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1069600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1082100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1048000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1054000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1023400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1052400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1039100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1056300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1053400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1062800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1084400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1108800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1098800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1085800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1071000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1061400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1007300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1011500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1001000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4675,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,111 +4709,115 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E57" s="3">
         <v>52500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>74400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>45100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>53800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>48400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>50700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>46400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>52500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>51200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>50200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>47300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>39300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>43300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>48000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>33700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>38900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>40700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>43200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>40600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>37700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>38700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>37200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>39800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>34900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>39300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>42000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>52900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>42700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>43100</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>24</v>
@@ -4700,8 +4834,8 @@
       <c r="L58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4719,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>18300</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>18300</v>
@@ -4734,387 +4868,402 @@
         <v>18300</v>
       </c>
       <c r="X58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="Y58" s="3">
         <v>17300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>16400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>15400</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>14500</v>
       </c>
       <c r="AB58" s="3">
         <v>14500</v>
       </c>
       <c r="AC58" s="3">
-        <v>14400</v>
+        <v>14500</v>
       </c>
       <c r="AD58" s="3">
         <v>14400</v>
       </c>
       <c r="AE58" s="3">
+        <v>14400</v>
+      </c>
+      <c r="AF58" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E59" s="3">
         <v>215700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>192700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>253100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>95000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>86400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>62000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>77700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>77500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>63900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>45300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>59400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>58500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>62800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>48300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>50600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>49100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>53400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>44300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>68500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>61800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>60900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>59400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>73600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>64100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>79100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>51500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>66600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>239000</v>
+      </c>
+      <c r="E60" s="3">
         <v>321100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>309800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>396900</v>
-      </c>
-      <c r="G60" s="3">
-        <v>140100</v>
       </c>
       <c r="H60" s="3">
         <v>140100</v>
       </c>
       <c r="I60" s="3">
+        <v>140100</v>
+      </c>
+      <c r="J60" s="3">
         <v>110400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>128400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>123900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>116400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>96500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>109600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>105900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>102100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>91600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>98600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>101100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>110600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>103300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>129900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>120600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>115900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>114400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>126200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>118400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>128400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>105300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>123000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1373600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1330600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1336600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1297000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>455100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>171900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>181800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>171700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>175600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>175400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>175300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>179200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>183100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>187000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>190800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>194700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>179100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>183700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>188300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>192800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>197400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>202000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>206600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>211100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>215700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>219300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>222900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>226500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>228800</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>91100</v>
+      </c>
+      <c r="E62" s="3">
         <v>99900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>120400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>119800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>79000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>88700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>88500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>93100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>103400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>99600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>93300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>94400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>82400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>87300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>79200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>81800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>69900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>72500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>66600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>57400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>73400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>87600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>84500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>83400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>72200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>73800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>61900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>56800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5351,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5291,8 +5443,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5535,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1703900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1751800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1767000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1813800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>674400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>401000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>380900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>393300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>403100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>391600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>365300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>383400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>371600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>376500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>361900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>375500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>350400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>366800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>358200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>380200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>391400</v>
-      </c>
-      <c r="X66" s="3">
-        <v>405500</v>
       </c>
       <c r="Y66" s="3">
         <v>405500</v>
       </c>
       <c r="Z66" s="3">
+        <v>405500</v>
+      </c>
+      <c r="AA66" s="3">
         <v>420800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>406300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>421500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>390100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>406300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>415200</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5663,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5753,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +5845,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +5937,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6029,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>408600</v>
+      </c>
+      <c r="E72" s="3">
         <v>446800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>828800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>858200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>909300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>886500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>834900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>796900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>762100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>727600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>694700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>671200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>655500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>637100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>620900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>611600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>611200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>593600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>588200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>579700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>561600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>549400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>524200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>502300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>503600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>490300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>477700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>467900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6213,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6305,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6397,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>334300</v>
+      </c>
+      <c r="E76" s="3">
         <v>366800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>733000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>755900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>792400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>798900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>735000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>737600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>718200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>708400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>704300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>698700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>676400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>677500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>661500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>677000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>688700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>689500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>695200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>682600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>692900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>703300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>693400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>665000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>664700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>639900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>617100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>605300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>585900</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6581,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E80" s="2">
         <v>45137</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44955</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44864</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44682</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44591</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44409</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44318</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44129</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44038</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43947</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43856</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43765</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43674</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43583</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43492</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43401</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43310</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43219</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43128</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43037</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42946</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42764</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-382000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-29400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-51000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>22700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>51600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>38000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>34800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>34400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>32900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>23500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>15700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>14000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>12200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>25200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>12400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>13300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>11800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>8000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,97 +6806,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E83" s="3">
         <v>22000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>24500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>7300</v>
       </c>
       <c r="H83" s="3">
         <v>7300</v>
       </c>
       <c r="I83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J83" s="3">
         <v>7700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>9300</v>
-      </c>
-      <c r="S83" s="3">
-        <v>9700</v>
       </c>
       <c r="T83" s="3">
         <v>9700</v>
       </c>
       <c r="U83" s="3">
+        <v>9700</v>
+      </c>
+      <c r="V83" s="3">
         <v>10800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>13200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>11800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>11300</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>11600</v>
       </c>
       <c r="AE83" s="3">
         <v>11600</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +6988,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7080,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7172,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7264,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7356,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-12000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-90000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>77300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>50100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>51000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>66500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>53000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>32600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>27300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>28400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>37200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>26100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>45300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>33300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>33400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>47200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>52000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>49300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>35000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>38600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>26900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>35600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>10400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>32900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>39200</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,97 +7484,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-4900</v>
       </c>
       <c r="Y91" s="3">
         <v>-4900</v>
       </c>
       <c r="Z91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-13800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7666,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7758,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1246600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>20500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-34100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,8 +7886,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7742,8 +7976,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8068,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8160,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,108 +8252,114 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>33700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>883100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>248400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-44200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-37500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-38600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-41400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-34600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-36100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-38900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-30300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-32800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-24100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-15800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-36300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-47000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-30800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-600</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>24</v>
@@ -8127,8 +8376,8 @@
       <c r="K101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8187,93 +8436,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-71300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-382300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>255700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>87000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-24400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>10300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-24800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>8000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>16800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>59100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>SMTC</t>
   </si>
@@ -656,418 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45410</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45319</v>
+      </c>
+      <c r="F7" s="2">
         <v>45228</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45137</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44955</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44864</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44682</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44591</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44409</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44318</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44129</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44038</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43947</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43856</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43765</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43674</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43583</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43492</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43401</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43310</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43219</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43128</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43037</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42946</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42764</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>206100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>192900</v>
+      </c>
+      <c r="F8" s="3">
         <v>200900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>238400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>236500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>167500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>177600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>209300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>202100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>190600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>194900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>185000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>170400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>164700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>154100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>143700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>132700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>138000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>141000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>137100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>131400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>160000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>173600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>163200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>130400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>140600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>150300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>153100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>143800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>140000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>137200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>106500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>101500</v>
+      </c>
+      <c r="F9" s="3">
         <v>107900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>137300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>133100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>70300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>61900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>74500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>72900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>73400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>71200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>69600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>65500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>64200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>60000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>55400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>51900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>53700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>54800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>52300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>50100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>61100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>67000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>63100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>59000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>55200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>60900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>60900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>58900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>56500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>99600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>91400</v>
+      </c>
+      <c r="F10" s="3">
         <v>93000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>101100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>103400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>97200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>115700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>134800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>129200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>117200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>123700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>115400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>104900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>100500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>94100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>88300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>80800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>84300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>86200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>84800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>81300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>98900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>106600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>100100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>71400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>85400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>89400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>92200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>84900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>83500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1100,100 +1125,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E12" s="3">
         <v>46900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>46900</v>
+      </c>
+      <c r="G12" s="3">
         <v>47400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>50600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>52500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>35100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>40600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>38800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>38300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>37300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>35500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>36800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>32800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>27900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>29200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>27600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>28000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>27000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>25900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>27200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>27600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>27100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>28100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>26200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>23800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>27600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>27400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>26000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>25400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1284,192 +1317,210 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E14" s="3">
+        <v>610600</v>
+      </c>
+      <c r="F14" s="3">
         <v>7900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>289500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>2100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>11100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>9300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-18400</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>400</v>
-      </c>
-      <c r="L14" s="3">
-        <v>200</v>
-      </c>
-      <c r="M14" s="3">
-        <v>500</v>
       </c>
       <c r="N14" s="3">
         <v>200</v>
       </c>
       <c r="O14" s="3">
+        <v>500</v>
+      </c>
+      <c r="P14" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>3600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>1300</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>2000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>30100</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>5900</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>1800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>-25000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>4900</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>4900</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
         <v>4900</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>1000</v>
       </c>
       <c r="L15" s="3">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="N15" s="3">
         <v>1300</v>
       </c>
       <c r="O15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q15" s="3">
         <v>1600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>2000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>2800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>3700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>3800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>3900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>5100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>6700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>6500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>6500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>7000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>7500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>7500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>6700</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>6300</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>6300</v>
       </c>
       <c r="AF15" s="3">
         <v>6300</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1499,192 +1550,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>204100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>814600</v>
+      </c>
+      <c r="F17" s="3">
         <v>215300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>538700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>248500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>224700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>147500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>144800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>155100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>148000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>157700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>148800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>142600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>147000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>132900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>126400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>120600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>137700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>123100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>125400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>119200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>126200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>161700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>130300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>133500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>126600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>132700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>134200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>125500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>124700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>98100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-621700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-14400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-300300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-12000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-57200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>30100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>64500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>47000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>42600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>37200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>36200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>27800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>17700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>21200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>17300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>12100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>17900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>11700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>12200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>33800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>11900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>32900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>14000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>17600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>18900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>18300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>15300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>39100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1717,468 +1782,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F20" s="3">
         <v>6900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>2800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>5500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-900</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>200</v>
+        <v>-900</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
+        <v>200</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>1300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>3500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>1300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-611300</v>
+      </c>
+      <c r="F21" s="3">
         <v>15100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-276700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>15400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-41800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>38200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>72100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>54800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>49900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>44800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>44200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>35200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>25400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>28800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>24800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>21100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>9600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>28300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>22700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>26500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>48000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>25800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>45600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>9500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>25900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>31500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>30500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>28900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>26000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>50000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>25700</v>
+      </c>
+      <c r="F22" s="3">
         <v>31100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>26600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>22700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>8400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>1800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>1000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1200</v>
       </c>
       <c r="N22" s="3">
         <v>1200</v>
       </c>
       <c r="O22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>1000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>1600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>2200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>2600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>4900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>2500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>2400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>2200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>2200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>1900</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>2000</v>
       </c>
       <c r="AD22" s="3">
         <v>2000</v>
       </c>
       <c r="AE22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>3400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-645800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-38600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-325400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-31800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-60100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>29100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>63300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>46100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>41200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>36100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>35200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>26600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>16200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>19900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>15800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>11000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>16300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>10400</v>
-      </c>
-      <c r="V23" s="3">
-        <v>10700</v>
-      </c>
-      <c r="W23" s="3">
-        <v>33200</v>
       </c>
       <c r="X23" s="3">
         <v>10700</v>
       </c>
       <c r="Y23" s="3">
+        <v>33200</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>10700</v>
+      </c>
+      <c r="AA23" s="3">
         <v>31300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>10800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>16800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>16700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>15600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>11000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>36500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>56600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-9100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>6300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>12000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>8100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>6400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>3000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>3000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>3200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>1600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>2800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>2700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>8400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-2400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>6600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>3200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>6100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-17500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-52200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>3300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>4100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>3800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>3000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2269,192 +2366,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-642400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-38200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-382000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-29400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-51000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>22800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>51300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>38000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>34800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>33100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>32300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>23400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>15300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>18300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>16300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>9600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-4400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>13600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>13200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>26600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>7400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>25200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>12400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>63100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>13500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>12600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>11800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>8000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-642400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-38300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-382000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-29400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-51000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>22700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>51600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>38000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>34800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>34400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>32900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>23500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>15700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>18500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>16100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>9600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-4400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>14000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>2200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>12700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>26500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>7500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>25200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>12400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>63000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>13300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>12600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>11800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>8000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2545,8 +2660,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2589,11 +2710,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>24</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>24</v>
@@ -2607,26 +2728,26 @@
       <c r="V29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-6600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>4700</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>-64300</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
+      <c r="AC29" s="3">
+        <v>-64300</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -2637,8 +2758,14 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2729,8 +2856,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2821,192 +2954,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-6900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-2800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-5500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>900</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>-200</v>
+        <v>900</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-1300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-3500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-642400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-38300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-382000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-29400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-51000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>22700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>51600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>38000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>34800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>34400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>32900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>23500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>15700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>18500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>16100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>9600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-4400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>14000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>2200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>12700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>19900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>12200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>25200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>12400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>13300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>12600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>11800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>8000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3097,197 +3248,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-642400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-38300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-382000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-29400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-51000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>22700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>51600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>38000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>34800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>34400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>32900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>23500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>15700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>18500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>16100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>9600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-4400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>14000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>2200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>12700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>19900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>12200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>25200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>12400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>13300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>12600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>11800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>8000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45410</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45319</v>
+      </c>
+      <c r="F38" s="2">
         <v>45228</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45137</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44955</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44864</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44682</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44591</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44409</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44318</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44129</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44038</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43947</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43856</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43765</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43674</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43583</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43492</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43401</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43310</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43219</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43128</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43037</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42946</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42764</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3320,8 +3489,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3354,100 +3525,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>126800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>128600</v>
+      </c>
+      <c r="F41" s="3">
         <v>123800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>147900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>164200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>235500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>617800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>362200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>275200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>279600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>276600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>262700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>258200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>268900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>262300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>281500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>268900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>293300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>283100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>287800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>287300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>312100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>312200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>311300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>303300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>307900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>291100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>277900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>281600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>297100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>297900</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3538,376 +3717,406 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>153900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>134300</v>
+      </c>
+      <c r="F43" s="3">
         <v>156600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>159100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>145400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>161700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>80500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>71100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>66400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>71500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>74300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>73100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>66500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>70400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>58700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>51700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>49500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>61900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>61400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>58600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>66500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>79200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>83800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>78400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>65600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>53200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>66500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>61200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>55900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>51400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>148500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>145000</v>
+      </c>
+      <c r="F44" s="3">
         <v>160600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>180200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>213200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>207700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>111100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>107600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>106900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>114000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>105200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>103000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>93900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>87500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>78400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>77500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>76900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>73000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>70100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>75100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>73500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>63700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>61200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>58900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>65500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>71100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>71200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>75000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>76800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>65900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>62700</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>126300</v>
+      </c>
+      <c r="F45" s="3">
         <v>131400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>142700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>141600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>117900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>25800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>36200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>47000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>37200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>40300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>46100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>42700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>47900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>48400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>43200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>37000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>32500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>25400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>31700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>29800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>30300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>29200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>29700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>33000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>29100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>21000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>24800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>21500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>24000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>539300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>534200</v>
+      </c>
+      <c r="F46" s="3">
         <v>572400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>629900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>664400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>722800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>835200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>577100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>495400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>502300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>496400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>484800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>461400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>474700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>447700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>453900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>432300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>460700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>440000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>453300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>457000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>485300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>486400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>478300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>467400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>461200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>449800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>438800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>435700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>438400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3989,201 +4198,219 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-      <c r="AD47" s="3" t="s">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE47" s="3" t="s">
+      <c r="AG47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>169800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>177500</v>
+      </c>
+      <c r="F48" s="3">
         <v>158800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>192200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>195200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>201100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>153700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>153500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>152700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>154700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>151400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>153700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>146600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>147300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>139600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>142700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>141700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>135400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>134200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>136700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>138200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>118500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>119500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>122600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>122500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>124600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>123400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>118700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>110300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>108900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>95500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>576000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>576800</v>
+      </c>
+      <c r="F49" s="3">
         <v>1181900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1200800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1487600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1496800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>354000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>355000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>356100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>357900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>359000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>360300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>361600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>362900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>364500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>366300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>368300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>371200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>374900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>378600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>382600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>387700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>395500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>393500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>395100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>402100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>409600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>421700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>385200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>391500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>397800</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4274,8 +4501,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4366,100 +4599,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>91500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>85300</v>
+      </c>
+      <c r="F52" s="3">
         <v>125000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>95600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>152800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>148900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>123900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>114300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>111700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>116000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>114500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>101200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>100100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>97200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>96100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>91100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>81000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>85200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>90100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>87700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>75700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>71300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>83000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>114400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>113800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>97900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>88200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>82100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>76100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>72700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4550,100 +4795,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1376500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1373700</v>
+      </c>
+      <c r="F54" s="3">
         <v>2038100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2118600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2500000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2569600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1466900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1199800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1115900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1130900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1121300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1100000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1069600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1082100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1048000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1054000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1023400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1052400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1039100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1056300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1053400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1062800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1084400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1108800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1098800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1085800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1071000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1061400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1007300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1011500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1001000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4676,8 +4933,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4710,120 +4969,128 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>64700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>45100</v>
+      </c>
+      <c r="F57" s="3">
         <v>55000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>52500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>74400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>100700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>45100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>53800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>48400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>50700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>46400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>52500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>51200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>50200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>47300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>39300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>43300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>48000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>33700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>38900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>40700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>43200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>40600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>37700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>38700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>37200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>39800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>34900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>39300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>42000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>52900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>42700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>43100</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>24</v>
@@ -4837,11 +5104,11 @@
       <c r="M58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4856,10 +5123,10 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>18300</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>18300</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
         <v>18300</v>
@@ -4871,399 +5138,429 @@
         <v>18300</v>
       </c>
       <c r="Y58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="AA58" s="3">
         <v>17300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>16400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>15400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>14500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>14500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>14400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>14400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>160200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>172100</v>
+      </c>
+      <c r="F59" s="3">
         <v>184000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>215700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>192700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>253100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>95000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>86400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>62000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>77700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>77500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>63900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>45300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>59400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>58500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>62800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>48300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>50600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>49100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>53400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>44300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>68500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>61800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>60900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>59400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>73600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>64100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>79100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>51500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>66600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>224900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>217200</v>
+      </c>
+      <c r="F60" s="3">
         <v>239000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>321100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>309800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>396900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>140100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>140100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>110400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>128400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>123900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>116400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>96500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>109600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>105900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>102100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>91600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>98600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>101100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>110600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>103300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>129900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>120600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>115900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>114400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>126200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>118400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>128400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>105300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>123000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1373400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1371000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1373600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1330600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1336600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1297000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>455100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>171900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>181800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>171700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>175600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>175400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>175300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>179200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>183100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>187000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>190800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>194700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>179100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>183700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>188300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>192800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>197400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>202000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>206600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>211100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>215700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>219300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>222900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>226500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>228800</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>92800</v>
+      </c>
+      <c r="F62" s="3">
         <v>91100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>99900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>120400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>119800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>79000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>88700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>88500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>93100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>103400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>99600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>93300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>94400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>82400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>87300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>79200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>81800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>69900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>72500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>66600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>57400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>73400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>87600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>84500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>83400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>72200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>73800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>61900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>56800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5354,8 +5651,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5446,8 +5749,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5538,100 +5847,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1689600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1681200</v>
+      </c>
+      <c r="F66" s="3">
         <v>1703900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1751800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1767000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1813800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>674400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>401000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>380900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>393300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>403100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>391600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>365300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>383400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>371600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>376500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>361900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>375500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>350400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>366800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>358200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>380200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>391400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>405500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>405500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>420800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>406300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>421500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>390100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>406300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>415200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5664,8 +5985,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5756,8 +6079,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5848,8 +6177,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5940,8 +6275,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6032,100 +6373,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-256900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-233800</v>
+      </c>
+      <c r="F72" s="3">
         <v>408600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>446800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>828800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>858200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>909300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>886500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>834900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>796900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>762100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>727600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>694700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>671200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>655500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>637100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>620900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>611600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>611200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>593600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>588200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>579700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>561600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>549400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>524200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>502300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>503600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>490300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>477700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>467900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6216,8 +6569,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6308,8 +6667,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6400,100 +6765,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-313100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-307400</v>
+      </c>
+      <c r="F76" s="3">
         <v>334300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>366800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>733000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>755900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>792400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>798900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>735000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>737600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>718200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>708400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>704300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>698700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>676400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>677500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>661500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>677000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>688700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>689500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>695200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>682600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>692900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>703300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>693400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>665000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>664700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>639900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>617100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>605300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>585900</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6584,197 +6961,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45410</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45319</v>
+      </c>
+      <c r="F80" s="2">
         <v>45228</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45137</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44955</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44864</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44682</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44591</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44409</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44318</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44129</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44038</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43947</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43856</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43765</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43674</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43583</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43492</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43401</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43310</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43219</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43128</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43037</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42946</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42764</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-642400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-38300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-382000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-29400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-51000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>22700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>51600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>38000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>34800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>34400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>32900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>23500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>15700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>18500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>16100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>9600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-4400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>14000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>2200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>12700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>19900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>12200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>25200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>12400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>13300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>12600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>11800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>8000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6807,100 +7202,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F83" s="3">
         <v>22500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>22000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>24500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>9800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>7300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>7300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>7700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>8200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>7500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>7800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>7400</v>
-      </c>
-      <c r="O83" s="3">
-        <v>7700</v>
-      </c>
-      <c r="P83" s="3">
-        <v>7900</v>
       </c>
       <c r="Q83" s="3">
         <v>7700</v>
       </c>
       <c r="R83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="S83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="T83" s="3">
         <v>8500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>9300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>9700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>9700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>10800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>12300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>12800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>12100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>12500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>13200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>12700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>11800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>11300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>11600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6991,8 +7394,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7083,8 +7492,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7175,8 +7590,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7267,8 +7688,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7359,100 +7786,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-12000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-90000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-18800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>18200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>77300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>50100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>51000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>66500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>53000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>32600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>27300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>28400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>37200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>26100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>45300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>33300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>33400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>6700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>47200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>52000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>49300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>35000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>38600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>26900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>35600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>10400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>32900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>39200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7485,100 +7924,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-7100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-7200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-14000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-5700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-7100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-7300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-8300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-8100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-5300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-7000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-5800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-10900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-7700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-2600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-3500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-1600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-15300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-4100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-13800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7669,8 +8116,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7761,100 +8214,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-6700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-5200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-14400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1246600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-11000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>20500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-10300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-10500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-14000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-7200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-8700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-10500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-9400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-11600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-4700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-5200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-8700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-15800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-11000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-12300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-34100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7887,8 +8352,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7979,8 +8446,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8071,8 +8544,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8163,8 +8642,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8255,117 +8740,129 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-10400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>33700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>883100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>248400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-10800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-44200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-37500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-38600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-41400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-34600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-10100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-15300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-38900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-30300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-32800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-24100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-15800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-36300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-47000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-30800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>24</v>
@@ -8379,11 +8876,11 @@
       <c r="L101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -8439,96 +8936,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-24100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-16300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-71300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-382300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>255700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>87000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>13900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>4400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-10700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>6600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>12500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-24400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>10300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-4800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-24800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>8000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>16800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>13300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>59100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>SMTC</t>
   </si>
@@ -656,443 +656,456 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45501</v>
+      </c>
+      <c r="E7" s="2">
         <v>45410</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45319</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45228</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45137</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44955</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44864</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44682</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44591</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44409</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44318</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44129</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44038</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43947</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43856</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43765</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43674</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43583</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43492</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43401</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43310</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43219</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43128</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43037</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42946</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42764</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>215400</v>
+      </c>
+      <c r="E8" s="3">
         <v>206100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>192900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>238400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>236500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>167500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>177600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>209300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>202100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>190600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>194900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>185000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>170400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>164700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>154100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>143700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>132700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>138000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>141000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>137100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>131400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>160000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>173600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>163200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>130400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>140600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>150300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>153100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>143800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>140000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>137200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>109900</v>
+      </c>
+      <c r="E9" s="3">
         <v>106500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>101500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>107900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>137300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>133100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>70300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>61900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>74500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>72900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>73400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>71200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>69600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>65500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>64200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>60000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>55400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>51900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>53700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>54800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>52300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>50100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>61100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>67000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>63100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>59000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>55200</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>60900</v>
       </c>
       <c r="AE9" s="3">
         <v>60900</v>
       </c>
       <c r="AF9" s="3">
+        <v>60900</v>
+      </c>
+      <c r="AG9" s="3">
         <v>58900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>56500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>105500</v>
+      </c>
+      <c r="E10" s="3">
         <v>99600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>91400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>93000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>101100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>103400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>97200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>115700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>134800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>129200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>117200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>123700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>115400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>104900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>100500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>94100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>88300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>80800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>84300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>86200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>84800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>81300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>98900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>106600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>100100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>71400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>85400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>89400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>92200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>84900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>83500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,106 +1140,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E12" s="3">
         <v>41600</v>
-      </c>
-      <c r="E12" s="3">
-        <v>46900</v>
       </c>
       <c r="F12" s="3">
         <v>46900</v>
       </c>
       <c r="G12" s="3">
+        <v>46900</v>
+      </c>
+      <c r="H12" s="3">
         <v>47400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>50600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>52500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>35100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>40600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>38800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>38300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>37300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>35500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>36800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>32800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>27900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>29200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>27600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>28000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>27000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>25900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>27200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>27600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>27100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>28100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>26200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>23800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>27600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>27400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>26000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>25400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1323,106 +1340,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>146200</v>
+      </c>
+      <c r="E14" s="3">
         <v>3400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>610600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>289500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-18400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1300</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>2000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>30100</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5900</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-25000</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1433,7 +1456,7 @@
         <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>4900</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>4900</v>
@@ -1441,23 +1464,23 @@
       <c r="H15" s="3">
         <v>4900</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1000</v>
       </c>
       <c r="K15" s="3">
         <v>1000</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>1000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1300</v>
       </c>
       <c r="O15" s="3">
         <v>1300</v>
@@ -1466,52 +1489,52 @@
         <v>1300</v>
       </c>
       <c r="Q15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R15" s="3">
         <v>1600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>5100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>6700</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>6500</v>
       </c>
       <c r="AA15" s="3">
         <v>6500</v>
       </c>
       <c r="AB15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="AC15" s="3">
         <v>7000</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>7500</v>
       </c>
       <c r="AD15" s="3">
         <v>7500</v>
       </c>
       <c r="AE15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AF15" s="3">
         <v>6700</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>6300</v>
       </c>
       <c r="AG15" s="3">
         <v>6300</v>
@@ -1519,8 +1542,11 @@
       <c r="AH15" s="3">
         <v>6300</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1552,204 +1578,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>352300</v>
+      </c>
+      <c r="E17" s="3">
         <v>204100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>814600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>215300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>538700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>248500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>224700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>147500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>144800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>155100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>148000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>157700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>148800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>142600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>147000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>132900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>126400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>120600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>137700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>123100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>125400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>119200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>126200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>161700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>130300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>133500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>126600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>132700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>134200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>125500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>124700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>98100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-136900</v>
+      </c>
+      <c r="E18" s="3">
         <v>2000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-621700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-300300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-57200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>64500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>47000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>42600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>37200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>36200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>27800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>21200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>33800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>32900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>14000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>17600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>18900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>18300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>15300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>39100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1784,239 +1817,246 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>3700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-122100</v>
+      </c>
+      <c r="E21" s="3">
         <v>16300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-611300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-276700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>15400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-41800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>38200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>72100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>54800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>49900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>44800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>44200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>35200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>25400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>28800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>21100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>28300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>22700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>26500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>48000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>25800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>45600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>25900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>31500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>30500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>28900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>26000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>50000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E22" s="3">
         <v>26000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>31100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>26600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1200</v>
       </c>
       <c r="O22" s="3">
         <v>1200</v>
@@ -2025,46 +2065,46 @@
         <v>1200</v>
       </c>
       <c r="Q22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R22" s="3">
         <v>1500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2400</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>2200</v>
       </c>
       <c r="AB22" s="3">
         <v>2200</v>
       </c>
       <c r="AC22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AD22" s="3">
         <v>1900</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>2000</v>
       </c>
       <c r="AE22" s="3">
         <v>2000</v>
@@ -2073,209 +2113,218 @@
         <v>2000</v>
       </c>
       <c r="AG22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>3400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-166100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-20300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-645800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-38600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-325400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-31800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-60100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>63300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>46100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>41200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>36100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>35200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>26600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>16200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>19900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>15800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>11000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>16300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>10700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>33200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>10700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>31300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>16800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>16700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>15600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>11000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>36500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E24" s="3">
         <v>3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>56600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-9100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6400</v>
-      </c>
-      <c r="N24" s="3">
-        <v>3000</v>
       </c>
       <c r="O24" s="3">
         <v>3000</v>
       </c>
       <c r="P24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q24" s="3">
         <v>3200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>8400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-17500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-52200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2372,204 +2421,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-170300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-642400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-382000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-29400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-51000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>51300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>38000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>34800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>33100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>32300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>23400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>15300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>18300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>13600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>13200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>26600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>25200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>12400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>63100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>13500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>12600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>11800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>8000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-170300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-642400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-382000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-29400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-51000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>22700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>51600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>38000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>34800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>34400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>32900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>23500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>15700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>14000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>12700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>26500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>7500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>25200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>63000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>13300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>12600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>11800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>8000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2666,8 +2724,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2716,8 +2777,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>24</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>24</v>
@@ -2734,23 +2795,23 @@
       <c r="X29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>4700</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-64300</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -2764,8 +2825,11 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2862,8 +2926,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2960,204 +3027,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-170300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-642400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-382000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-29400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-51000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>22700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>51600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>38000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>34800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>34400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>32900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>23500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>15700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>14000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>12700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>12200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>25200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>13300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>12600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>11800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>8000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3254,209 +3330,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-170300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-642400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-382000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-29400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-51000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>22700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>51600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>38000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>34800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>34400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>32900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>23500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>15700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>14000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>12700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>12200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>25200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>13300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>12600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>11800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>8000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45501</v>
+      </c>
+      <c r="E38" s="2">
         <v>45410</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45319</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45228</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45137</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44955</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44864</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44682</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44591</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44409</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44318</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44129</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44038</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43947</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43856</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43765</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43674</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43583</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43492</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43401</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43310</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43219</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43128</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43037</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42946</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42764</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3491,8 +3576,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3527,106 +3613,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>115900</v>
+      </c>
+      <c r="E41" s="3">
         <v>126800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>128600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>123800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>147900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>164200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>235500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>617800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>362200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>275200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>279600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>276600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>262700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>258200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>268900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>262300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>281500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>268900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>293300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>283100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>287800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>287300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>312100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>312200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>311300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>303300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>307900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>291100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>277900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>281600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>297100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>297900</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3723,400 +3813,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E43" s="3">
         <v>153900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>134300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>156600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>159100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>145400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>161700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>80500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>71100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>66400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>71500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>74300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>73100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>66500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>70400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>58700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>51700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>49500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>61900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>61400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>58600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>66500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>79200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>83800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>78400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>65600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>53200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>66500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>61200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>55900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>51400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E44" s="3">
         <v>148500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>145000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>160600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>180200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>213200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>207700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>111100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>107600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>106900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>114000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>105200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>103000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>93900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>87500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>78400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>77500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>76900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>73000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>70100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>75100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>73500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>63700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>61200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>58900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>65500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>71100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>71200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>75000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>76800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>65900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>62700</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>116800</v>
+      </c>
+      <c r="E45" s="3">
         <v>110000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>126300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>131400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>142700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>141600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>117900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>25800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>36200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>47000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>37200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>40300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>46100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>42700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>47900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>48400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>43200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>37000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>32500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>25400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>31700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>29800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>30300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>29200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>29700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>33000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>29100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>21000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>24800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>21500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>24000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>541700</v>
+      </c>
+      <c r="E46" s="3">
         <v>539300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>534200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>572400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>629900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>664400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>722800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>835200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>577100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>495400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>502300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>496400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>484800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>461400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>474700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>447700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>453900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>432300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>460700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>440000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>453300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>457000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>485300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>486400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>478300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>467400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>461200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>449800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>438800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>435700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>438400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4204,213 +4309,222 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>24</v>
+      <c r="AF47" s="3">
+        <v>0</v>
       </c>
       <c r="AG47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AH47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI47" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E48" s="3">
         <v>169800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>177500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>158800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>192200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>195200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>201100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>153700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>153500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>152700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>154700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>151400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>153700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>146600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>147300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>139600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>142700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>141700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>135400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>134200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>136700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>138200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>118500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>119500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>122600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>122500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>124600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>123400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>118700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>110300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>108900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>95500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>576500</v>
+      </c>
+      <c r="E49" s="3">
         <v>576000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>576800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1181900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1200800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1487600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1496800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>354000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>355000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>356100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>357900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>359000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>360300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>361600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>362900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>364500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>366300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>368300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>371200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>374900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>378600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>382600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>387700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>395500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>393500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>395100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>402100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>409600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>421700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>385200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>391500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>397800</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4507,8 +4621,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4605,106 +4722,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>86800</v>
+      </c>
+      <c r="E52" s="3">
         <v>91500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>85300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>125000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>95600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>152800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>148900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>123900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>114300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>111700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>116000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>114500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>101200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>100100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>97200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>96100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>91100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>81000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>85200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>90100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>87700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>75700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>71300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>83000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>114400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>113800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>97900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>88200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>82100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>76100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>72700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4801,106 +4924,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1368000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1376500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1373700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2038100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2118600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2500000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2569600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1466900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1199800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1115900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1130900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1121300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1100000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1069600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1082100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1048000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1054000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1023400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1052400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1039100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1056300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1053400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1062800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1084400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1108800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1098800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1085800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1071000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1061400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1007300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1011500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1001000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4935,8 +5064,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4971,129 +5101,133 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E57" s="3">
         <v>64700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>45100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>55000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>52500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>74400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>45100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>53800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>48400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>50700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>46400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>52500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>51200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>50200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>47300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>39300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>43300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>48000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>33700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>38900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>40700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>43200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>40600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>37700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>38700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>37200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>39800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>34900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>39300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>42000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
+      <c r="E58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>52900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>42700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>43100</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>24</v>
@@ -5110,8 +5244,8 @@
       <c r="O58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -5129,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
-        <v>18300</v>
+        <v>0</v>
       </c>
       <c r="W58" s="3">
         <v>18300</v>
@@ -5144,423 +5278,438 @@
         <v>18300</v>
       </c>
       <c r="AA58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="AB58" s="3">
         <v>17300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>16400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>15400</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>14500</v>
       </c>
       <c r="AE58" s="3">
         <v>14500</v>
       </c>
       <c r="AF58" s="3">
-        <v>14400</v>
+        <v>14500</v>
       </c>
       <c r="AG58" s="3">
         <v>14400</v>
       </c>
       <c r="AH58" s="3">
+        <v>14400</v>
+      </c>
+      <c r="AI58" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>148900</v>
+      </c>
+      <c r="E59" s="3">
         <v>160200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>172100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>184000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>215700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>192700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>253100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>95000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>86400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>62000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>77700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>77500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>63900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>45300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>59400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>58500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>62800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>48300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>50600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>49100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>53400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>44300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>68500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>61800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>60900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>59400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>73600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>64100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>79100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>51500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>66600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>224700</v>
+      </c>
+      <c r="E60" s="3">
         <v>224900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>217200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>239000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>321100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>309800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>396900</v>
-      </c>
-      <c r="J60" s="3">
-        <v>140100</v>
       </c>
       <c r="K60" s="3">
         <v>140100</v>
       </c>
       <c r="L60" s="3">
+        <v>140100</v>
+      </c>
+      <c r="M60" s="3">
         <v>110400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>128400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>123900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>116400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>96500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>109600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>105900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>102100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>91600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>98600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>101100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>110600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>103300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>129900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>120600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>115900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>114400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>126200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>118400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>128400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>105300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>123000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1192900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1373400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1371000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1373600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1330600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1336600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1297000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>455100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>171900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>181800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>171700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>175600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>175400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>175300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>179200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>183100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>187000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>190800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>194700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>179100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>183700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>188300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>192800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>197400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>202000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>206600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>211100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>215700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>219300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>222900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>226500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>228800</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E62" s="3">
         <v>91300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>92800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>91100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>99900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>120400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>119800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>79000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>88700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>88500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>93100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>103400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>99600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>93300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>94400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>82400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>87300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>79200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>81800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>69900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>72500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>66600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>57400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>73400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>87600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>84500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>83400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>72200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>73800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>61900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>56800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5657,8 +5806,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5755,8 +5907,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5853,106 +6008,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1509400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1689600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1681200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1703900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1751800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1767000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1813800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>674400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>401000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>380900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>393300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>403100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>391600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>365300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>383400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>371600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>376500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>361900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>375500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>350400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>366800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>358200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>380200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>391400</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>405500</v>
       </c>
       <c r="AB66" s="3">
         <v>405500</v>
       </c>
       <c r="AC66" s="3">
+        <v>405500</v>
+      </c>
+      <c r="AD66" s="3">
         <v>420800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>406300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>421500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>390100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>406300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>415200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5987,8 +6148,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6085,8 +6247,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6183,8 +6348,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6281,8 +6449,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6379,106 +6550,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-427200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-256900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-233800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>408600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>446800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>828800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>858200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>909300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>886500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>834900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>796900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>762100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>727600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>694700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>671200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>655500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>637100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>620900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>611600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>611200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>593600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>588200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>579700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>561600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>549400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>524200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>502300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>503600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>490300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>477700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>467900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6575,8 +6752,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6673,8 +6853,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6771,106 +6954,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-141400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-313100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-307400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>334300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>366800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>733000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>755900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>792400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>798900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>735000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>737600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>718200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>708400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>704300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>698700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>676400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>677500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>661500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>677000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>688700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>689500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>695200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>682600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>692900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>703300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>693400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>665000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>664700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>639900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>617100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>605300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>585900</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6967,209 +7156,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45501</v>
+      </c>
+      <c r="E80" s="2">
         <v>45410</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45319</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45228</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45137</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44955</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44864</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44682</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44591</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44409</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44318</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44129</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44038</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43947</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43856</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43765</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43674</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43583</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43492</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43401</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43310</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43219</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43128</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43037</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42946</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42764</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-170300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-642400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-382000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-29400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-51000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>22700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>51600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>38000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>34800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>34400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>32900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>23500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>15700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>14000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>12700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>12200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>25200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>13300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>12600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>11800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>8000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7204,106 +7402,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E83" s="3">
         <v>10500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>22500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>22000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>7300</v>
       </c>
       <c r="K83" s="3">
         <v>7300</v>
       </c>
       <c r="L83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="M83" s="3">
         <v>7700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9300</v>
-      </c>
-      <c r="V83" s="3">
-        <v>9700</v>
       </c>
       <c r="W83" s="3">
         <v>9700</v>
       </c>
       <c r="X83" s="3">
+        <v>9700</v>
+      </c>
+      <c r="Y83" s="3">
         <v>10800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>13200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>11800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>11300</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>11600</v>
       </c>
       <c r="AH83" s="3">
         <v>11600</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7400,8 +7602,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7498,8 +7703,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7596,8 +7804,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7694,8 +7905,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7792,106 +8006,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-12000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-90000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>77300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>50100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>51000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>66500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>53000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>32600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>27300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>37200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>26100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>45300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>33300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>33400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>47200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>52000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>49300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>35000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>38600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>26900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>35600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>10400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>32900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>39200</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7926,106 +8146,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-15300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-4900</v>
       </c>
       <c r="AB91" s="3">
         <v>-4900</v>
       </c>
       <c r="AC91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8122,8 +8346,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8220,106 +8447,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E94" s="3">
         <v>1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1246600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>20500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-8700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-15800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-34100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8354,8 +8587,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8452,8 +8686,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8550,8 +8787,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8648,8 +8888,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8746,126 +8989,132 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>33700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>883100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>248400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-44200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-37500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-38600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-41400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-10100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-36100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-15300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-38900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-30300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-32800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-24100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-15800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-36300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-47000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-30800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>24</v>
@@ -8882,8 +9131,8 @@
       <c r="N101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8942,102 +9191,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-24100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-71300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-382300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>255700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>87000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-19200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>12500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-24400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>10300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-24800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>8000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>16800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>13300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>59100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>SMTC</t>
   </si>
@@ -656,456 +656,469 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45592</v>
+      </c>
+      <c r="E7" s="2">
         <v>45501</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45410</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45319</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45228</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45137</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44955</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44864</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44682</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44591</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44409</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44318</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44129</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44038</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43947</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43856</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43765</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43674</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43583</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43492</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43401</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43310</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43219</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43128</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43037</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42946</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42764</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>236800</v>
+      </c>
+      <c r="E8" s="3">
         <v>215400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>206100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>192900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>238400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>236500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>167500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>177600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>209300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>202100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>190600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>194900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>185000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>170400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>164700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>154100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>143700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>132700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>138000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>141000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>137100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>131400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>160000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>173600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>163200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>130400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>140600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>150300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>153100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>143800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>140000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>137200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>109900</v>
+        <v>113600</v>
       </c>
       <c r="E9" s="3">
-        <v>106500</v>
+        <v>107600</v>
       </c>
       <c r="F9" s="3">
-        <v>101500</v>
+        <v>104200</v>
       </c>
       <c r="G9" s="3">
-        <v>107900</v>
+        <v>99300</v>
       </c>
       <c r="H9" s="3">
-        <v>137300</v>
+        <v>97900</v>
       </c>
       <c r="I9" s="3">
-        <v>133100</v>
+        <v>126700</v>
       </c>
       <c r="J9" s="3">
+        <v>122200</v>
+      </c>
+      <c r="K9" s="3">
         <v>70300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>61900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>74500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>72900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>73400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>71200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>69600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>65500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>64200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>60000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>55400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>51900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>53700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>54800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>52300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>50100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>61100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>67000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>63100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>59000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>55200</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>60900</v>
       </c>
       <c r="AF9" s="3">
         <v>60900</v>
       </c>
       <c r="AG9" s="3">
+        <v>60900</v>
+      </c>
+      <c r="AH9" s="3">
         <v>58900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>56500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>105500</v>
+        <v>123200</v>
       </c>
       <c r="E10" s="3">
-        <v>99600</v>
+        <v>107700</v>
       </c>
       <c r="F10" s="3">
-        <v>91400</v>
+        <v>101900</v>
       </c>
       <c r="G10" s="3">
-        <v>93000</v>
+        <v>93700</v>
       </c>
       <c r="H10" s="3">
-        <v>101100</v>
+        <v>103000</v>
       </c>
       <c r="I10" s="3">
-        <v>103400</v>
+        <v>111700</v>
       </c>
       <c r="J10" s="3">
+        <v>114300</v>
+      </c>
+      <c r="K10" s="3">
         <v>97200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>115700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>134800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>129200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>117200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>123700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>115400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>104900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>100500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>94100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>88300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>80800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>84300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>86200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>84800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>81300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>98900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>106600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>100100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>71400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>85400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>89400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>92200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>84900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>83500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1141,109 +1154,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E12" s="3">
         <v>40100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>41600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
+        <v>41500</v>
+      </c>
+      <c r="H12" s="3">
         <v>46900</v>
       </c>
-      <c r="G12" s="3">
-        <v>46900</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>47400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>50600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>52500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>35100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>40600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>38800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>38300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>37300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>35500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>36800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>32800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>27900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>29200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>27600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>28000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>27000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>25900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>27200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>27600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>27100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>28100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>26200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>23800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>27600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>27400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>26000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>25400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1343,147 +1360,153 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3">
         <v>146200</v>
       </c>
-      <c r="E14" s="3">
-        <v>3400</v>
-      </c>
       <c r="F14" s="3">
-        <v>610600</v>
+        <v>8600</v>
       </c>
       <c r="G14" s="3">
+        <v>616000</v>
+      </c>
+      <c r="H14" s="3">
         <v>7900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>289500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-18400</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1300</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>2000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>30100</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5900</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-25000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>2400</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>2600</v>
       </c>
       <c r="F15" s="3">
-        <v>300</v>
+        <v>2600</v>
       </c>
       <c r="G15" s="3">
-        <v>4900</v>
+        <v>2600</v>
       </c>
       <c r="H15" s="3">
-        <v>4900</v>
+        <v>14900</v>
       </c>
       <c r="I15" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J15" s="3" t="s">
+        <v>15400</v>
+      </c>
+      <c r="J15" s="3">
+        <v>15700</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1000</v>
       </c>
       <c r="L15" s="3">
         <v>1000</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>1000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>1300</v>
       </c>
       <c r="P15" s="3">
         <v>1300</v>
@@ -1492,52 +1515,52 @@
         <v>1300</v>
       </c>
       <c r="R15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S15" s="3">
         <v>1600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>5100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>6700</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>6500</v>
       </c>
       <c r="AB15" s="3">
         <v>6500</v>
       </c>
       <c r="AC15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="AD15" s="3">
         <v>7000</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>7500</v>
       </c>
       <c r="AE15" s="3">
         <v>7500</v>
       </c>
       <c r="AF15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AG15" s="3">
         <v>6700</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>6300</v>
       </c>
       <c r="AH15" s="3">
         <v>6300</v>
@@ -1545,8 +1568,11 @@
       <c r="AI15" s="3">
         <v>6300</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>6300</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1579,210 +1605,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>352300</v>
+        <v>218300</v>
       </c>
       <c r="E17" s="3">
-        <v>204100</v>
+        <v>206000</v>
       </c>
       <c r="F17" s="3">
-        <v>814600</v>
+        <v>195500</v>
       </c>
       <c r="G17" s="3">
-        <v>215300</v>
+        <v>198600</v>
       </c>
       <c r="H17" s="3">
-        <v>538700</v>
+        <v>207400</v>
       </c>
       <c r="I17" s="3">
-        <v>248500</v>
+        <v>249200</v>
       </c>
       <c r="J17" s="3">
+        <v>246400</v>
+      </c>
+      <c r="K17" s="3">
         <v>224700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>147500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>144800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>155100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>148000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>157700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>148800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>142600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>147000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>132900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>126400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>120600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>137700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>123100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>125400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>119200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>126200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>161700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>130300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>133500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>126600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>132700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>134200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>125500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>124700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>98100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-136900</v>
+        <v>18500</v>
       </c>
       <c r="E18" s="3">
-        <v>2000</v>
+        <v>9300</v>
       </c>
       <c r="F18" s="3">
-        <v>-621700</v>
+        <v>10600</v>
       </c>
       <c r="G18" s="3">
-        <v>-14400</v>
+        <v>-5600</v>
       </c>
       <c r="H18" s="3">
-        <v>-300300</v>
+        <v>-6500</v>
       </c>
       <c r="I18" s="3">
-        <v>-12000</v>
+        <v>-10800</v>
       </c>
       <c r="J18" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-57200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>30100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>64500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>47000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>42600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>37200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>36200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>27800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>21200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>33800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>32900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>14000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>17600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>18900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>18300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>15300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>39100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1818,248 +1851,255 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>2200</v>
+        <v>1100</v>
       </c>
       <c r="E20" s="3">
-        <v>3700</v>
+        <v>1000</v>
       </c>
       <c r="F20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
-        <v>6900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2800</v>
-      </c>
       <c r="J20" s="3">
+        <v>500</v>
+      </c>
+      <c r="K20" s="3">
         <v>5500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-122100</v>
+        <v>19800</v>
       </c>
       <c r="E21" s="3">
-        <v>16300</v>
+        <v>10900</v>
       </c>
       <c r="F21" s="3">
-        <v>-611300</v>
+        <v>13700</v>
       </c>
       <c r="G21" s="3">
-        <v>15100</v>
+        <v>-5000</v>
       </c>
       <c r="H21" s="3">
-        <v>-276700</v>
+        <v>11900</v>
       </c>
       <c r="I21" s="3">
-        <v>15400</v>
+        <v>3100</v>
       </c>
       <c r="J21" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-41800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>38200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>72100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>54800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>49900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>44800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>44200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>35200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>25400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>28800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>24800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>21100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>28300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>22700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>26500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>48000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>25800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>45600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>25900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>31500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>30500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>28900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>26000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>50000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>31400</v>
+        <v>20800</v>
       </c>
       <c r="E22" s="3">
-        <v>26000</v>
+        <v>28600</v>
       </c>
       <c r="F22" s="3">
-        <v>25700</v>
+        <v>23200</v>
       </c>
       <c r="G22" s="3">
-        <v>31100</v>
+        <v>22800</v>
       </c>
       <c r="H22" s="3">
-        <v>26600</v>
+        <v>28300</v>
       </c>
       <c r="I22" s="3">
-        <v>22700</v>
+        <v>24200</v>
       </c>
       <c r="J22" s="3">
+        <v>20500</v>
+      </c>
+      <c r="K22" s="3">
         <v>8400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1200</v>
       </c>
       <c r="P22" s="3">
         <v>1200</v>
@@ -2068,46 +2108,46 @@
         <v>1200</v>
       </c>
       <c r="R22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S22" s="3">
         <v>1500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2400</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>2200</v>
       </c>
       <c r="AC22" s="3">
         <v>2200</v>
       </c>
       <c r="AD22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AE22" s="3">
         <v>1900</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>2000</v>
       </c>
       <c r="AF22" s="3">
         <v>2000</v>
@@ -2116,215 +2156,224 @@
         <v>2000</v>
       </c>
       <c r="AH22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>3400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-166100</v>
       </c>
-      <c r="E23" s="3">
-        <v>-20300</v>
-      </c>
       <c r="F23" s="3">
-        <v>-645800</v>
+        <v>-20200</v>
       </c>
       <c r="G23" s="3">
+        <v>-645700</v>
+      </c>
+      <c r="H23" s="3">
         <v>-38600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-325400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-31800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-60100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>29100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>63300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>46100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>41200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>36100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>35200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>26600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>16200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>19900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>15800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>11000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>16300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>10400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>10700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>33200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>31300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>16800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>16700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>15600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>11000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>36500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>56600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-9100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6400</v>
-      </c>
-      <c r="O24" s="3">
-        <v>3000</v>
       </c>
       <c r="P24" s="3">
         <v>3000</v>
       </c>
       <c r="Q24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R24" s="3">
         <v>3200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-17500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-52200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2424,210 +2473,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-170300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-642400</v>
       </c>
-      <c r="G26" s="3">
-        <v>-38200</v>
-      </c>
       <c r="H26" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="I26" s="3">
         <v>-382000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-29400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-51000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>22800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>51300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>38000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>34800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>33100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>32300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>23400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>15300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>18300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>13600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>13200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>25200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>12400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>63100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>13500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>12600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>11800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>8000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-170300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-642400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-38300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-382000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-29400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-51000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>22700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>51600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>38000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>34800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>34400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>32900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>23500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>15700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>14000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>12700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>26500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>25200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>12400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>63000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>13300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>12600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>11800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>8000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2727,8 +2785,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2780,8 +2841,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>24</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>24</v>
@@ -2798,23 +2859,23 @@
       <c r="Y29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>4700</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-64300</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>24</v>
@@ -2828,8 +2889,11 @@
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2929,8 +2993,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3030,210 +3097,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2200</v>
+        <v>-1100</v>
       </c>
       <c r="E32" s="3">
-        <v>-3700</v>
+        <v>-1000</v>
       </c>
       <c r="F32" s="3">
+        <v>500</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-2800</v>
-      </c>
       <c r="J32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-5500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-170300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-642400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-38300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-382000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-29400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-51000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>22700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>51600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>38000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>34800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>34400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>32900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>23500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>15700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>14000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>12700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>19900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>12200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>25200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>13300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>12600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>11800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>8000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3333,215 +3409,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-170300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-642400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-38300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-382000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-29400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-51000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>22700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>51600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>38000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>34800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>34400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>32900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>23500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>15700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>14000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>12700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>19900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>12200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>25200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>13300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>12600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>11800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>8000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45592</v>
+      </c>
+      <c r="E38" s="2">
         <v>45501</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45410</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45319</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45228</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45137</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44955</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44864</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44682</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44591</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44409</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44318</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44129</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44038</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43947</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43856</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43765</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43674</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43583</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43492</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43401</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43310</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43219</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43128</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43037</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42946</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42764</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3577,8 +3662,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3614,132 +3700,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>136500</v>
+      </c>
+      <c r="E41" s="3">
         <v>115900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>126800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>128600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>123800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>147900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>164200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>235500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>617800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>362200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>275200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>279600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>276600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>262700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>258200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>268900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>262300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>281500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>268900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>293300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>283100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>287800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>287300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>312100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>312200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>311300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>303300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>307900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>291100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>277900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>281600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>297100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>297900</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>16100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>19100</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>14500</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>22600</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>22900</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>19800</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3816,435 +3906,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>142500</v>
+      </c>
+      <c r="E43" s="3">
         <v>153000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>153900</v>
       </c>
-      <c r="F43" s="3">
-        <v>134300</v>
-      </c>
       <c r="G43" s="3">
+        <v>151600</v>
+      </c>
+      <c r="H43" s="3">
         <v>156600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>159100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>145400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>161700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>80500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>71100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>66400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>71500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>74300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>73100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>66500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>70400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>58700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>51700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>49500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>61900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>61400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>58600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>66500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>79200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>83800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>78400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>65600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>53200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>66500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>61200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>55900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>51400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>163500</v>
+      </c>
+      <c r="E44" s="3">
         <v>156000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>148500</v>
       </c>
-      <c r="F44" s="3">
-        <v>145000</v>
-      </c>
       <c r="G44" s="3">
+        <v>189800</v>
+      </c>
+      <c r="H44" s="3">
         <v>160600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>180200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>213200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>207700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>111100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>107600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>106900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>114000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>105200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>103000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>93900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>87500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>78400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>77500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>76900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>73000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>70100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>75100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>73500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>63700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>61200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>58900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>65500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>71100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>71200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>75000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>76800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>65900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>62700</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>116800</v>
+        <v>91400</v>
       </c>
       <c r="E45" s="3">
-        <v>110000</v>
+        <v>82400</v>
       </c>
       <c r="F45" s="3">
-        <v>126300</v>
+        <v>78200</v>
       </c>
       <c r="G45" s="3">
-        <v>131400</v>
+        <v>12700</v>
       </c>
       <c r="H45" s="3">
-        <v>142700</v>
+        <v>98500</v>
       </c>
       <c r="I45" s="3">
-        <v>141600</v>
+        <v>112100</v>
       </c>
       <c r="J45" s="3">
+        <v>110200</v>
+      </c>
+      <c r="K45" s="3">
         <v>117900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>47000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>37200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>40300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>46100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>42700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>47900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>48400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>43200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>37000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>32500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>25400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>31700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>29800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>30300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>29200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>29700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>33000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>29100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>21000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>24800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>21500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>24000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>557800</v>
+      </c>
+      <c r="E46" s="3">
         <v>541700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>539300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>534200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>572400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>629900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>664400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>722800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>835200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>577100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>495400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>502300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>496400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>484800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>461400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>474700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>447700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>453900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>432300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>460700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>440000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>453300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>457000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>485300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>486400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>478300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>467400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>461200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>449800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>438800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>435700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>438400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>43100</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4312,219 +4417,228 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>24</v>
+      <c r="AG47" s="3">
+        <v>0</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>155500</v>
+      </c>
+      <c r="E48" s="3">
         <v>163000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>169800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>177500</v>
       </c>
-      <c r="G48" s="3">
-        <v>158800</v>
-      </c>
       <c r="H48" s="3">
+        <v>188100</v>
+      </c>
+      <c r="I48" s="3">
         <v>192200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>195200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>201100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>153700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>153500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>152700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>154700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>151400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>153700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>146600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>147300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>139600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>142700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>141700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>135400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>134200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>136700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>138200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>118500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>119500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>122600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>122500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>124600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>123400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>118700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>110300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>108900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>95500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>576500</v>
+        <v>576600</v>
       </c>
       <c r="E49" s="3">
+        <v>575000</v>
+      </c>
+      <c r="F49" s="3">
         <v>576000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>576800</v>
       </c>
-      <c r="G49" s="3">
-        <v>1181900</v>
-      </c>
       <c r="H49" s="3">
-        <v>1200800</v>
+        <v>1181100</v>
       </c>
       <c r="I49" s="3">
+        <v>1200600</v>
+      </c>
+      <c r="J49" s="3">
         <v>1487600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1496800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>354000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>355000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>356100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>357900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>359000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>360300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>361600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>362900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>364500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>366300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>368300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>371200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>374900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>378600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>382600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>387700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>395500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>393500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>395100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>402100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>409600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>421700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>385200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>391500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>397800</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4624,8 +4738,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4725,109 +4842,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>86800</v>
+        <v>68000</v>
       </c>
       <c r="E52" s="3">
-        <v>91500</v>
+        <v>67900</v>
       </c>
       <c r="F52" s="3">
-        <v>85300</v>
+        <v>66000</v>
       </c>
       <c r="G52" s="3">
-        <v>125000</v>
+        <v>24200</v>
       </c>
       <c r="H52" s="3">
-        <v>95600</v>
+        <v>71400</v>
       </c>
       <c r="I52" s="3">
-        <v>152800</v>
+        <v>76800</v>
       </c>
       <c r="J52" s="3">
+        <v>83800</v>
+      </c>
+      <c r="K52" s="3">
         <v>148900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>123900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>114300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>111700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>116000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>114500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>101200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>100100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>97200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>96100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>91100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>81000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>85200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>90100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>87700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>75700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>71300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>83000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>114400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>113800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>97900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>88200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>82100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>76100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>72700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4927,109 +5050,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1379000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1368000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1376500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1373700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2038100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2118600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2500000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2569600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1466900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1199800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1115900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1130900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1121300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1100000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1069600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1082100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1048000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1054000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1023400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1052400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1039100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1056300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1053400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1062800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1084400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1108800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1098800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1085800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1071000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1061400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1007300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1011500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1001000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5065,8 +5194,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5102,135 +5232,139 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E57" s="3">
         <v>75800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>64700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>45100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>55000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>52500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>74400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>100700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>45100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>53800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>48400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>50700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>46400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>52500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>51200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>50200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>47300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>39300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>43300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>48000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>33700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>38900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>40700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>43200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>40600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>37700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>38700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>37200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>39800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>34900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>39300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>42000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>24</v>
+      <c r="D58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="H58" s="3">
-        <v>52900</v>
+        <v>6200</v>
       </c>
       <c r="I58" s="3">
-        <v>42700</v>
+        <v>59300</v>
       </c>
       <c r="J58" s="3">
+        <v>48700</v>
+      </c>
+      <c r="K58" s="3">
         <v>43100</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>24</v>
@@ -5247,8 +5381,8 @@
       <c r="P58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5266,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
-        <v>18300</v>
+        <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>18300</v>
@@ -5281,435 +5415,450 @@
         <v>18300</v>
       </c>
       <c r="AB58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="AC58" s="3">
         <v>17300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>16400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>15400</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>14500</v>
       </c>
       <c r="AF58" s="3">
         <v>14500</v>
       </c>
       <c r="AG58" s="3">
-        <v>14400</v>
+        <v>14500</v>
       </c>
       <c r="AH58" s="3">
         <v>14400</v>
       </c>
       <c r="AI58" s="3">
+        <v>14400</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>148900</v>
+        <v>1400</v>
       </c>
       <c r="E59" s="3">
-        <v>160200</v>
+        <v>2100</v>
       </c>
       <c r="F59" s="3">
-        <v>172100</v>
+        <v>6300</v>
       </c>
       <c r="G59" s="3">
-        <v>184000</v>
+        <v>57000</v>
       </c>
       <c r="H59" s="3">
-        <v>215700</v>
+        <v>6200</v>
       </c>
       <c r="I59" s="3">
-        <v>192700</v>
+        <v>8800</v>
       </c>
       <c r="J59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K59" s="3">
         <v>253100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>95000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>86400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>62000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>77700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>77500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>63900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>45300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>59400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>58500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>62800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>50600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>49100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>53400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>44300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>68500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>61800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>60900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>59400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>73600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>64100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>79100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>51500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>66600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>235500</v>
+      </c>
+      <c r="E60" s="3">
         <v>224700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>224900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>217200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>239000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>321100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>309800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>396900</v>
-      </c>
-      <c r="K60" s="3">
-        <v>140100</v>
       </c>
       <c r="L60" s="3">
         <v>140100</v>
       </c>
       <c r="M60" s="3">
+        <v>140100</v>
+      </c>
+      <c r="N60" s="3">
         <v>110400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>128400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>123900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>116400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>96500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>109600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>105900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>102100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>91600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>98600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>101100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>110600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>103300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>129900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>120600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>115900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>114400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>126200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>118400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>128400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>105300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>123000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1192900</v>
+        <v>1209700</v>
       </c>
       <c r="E61" s="3">
-        <v>1373400</v>
+        <v>1213600</v>
       </c>
       <c r="F61" s="3">
-        <v>1371000</v>
+        <v>1393700</v>
       </c>
       <c r="G61" s="3">
-        <v>1373600</v>
+        <v>1393100</v>
       </c>
       <c r="H61" s="3">
-        <v>1330600</v>
+        <v>1397000</v>
       </c>
       <c r="I61" s="3">
-        <v>1336600</v>
+        <v>1356200</v>
       </c>
       <c r="J61" s="3">
+        <v>1370300</v>
+      </c>
+      <c r="K61" s="3">
         <v>1297000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>455100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>171900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>181800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>171700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>175600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>175400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>175300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>179200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>183100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>187000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>190800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>194700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>179100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>183700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>188300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>192800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>197400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>202000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>206600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>211100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>215700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>219300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>222900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>226500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>228800</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>91900</v>
+        <v>73500</v>
       </c>
       <c r="E62" s="3">
-        <v>91300</v>
+        <v>71200</v>
       </c>
       <c r="F62" s="3">
-        <v>92800</v>
+        <v>71000</v>
       </c>
       <c r="G62" s="3">
-        <v>91100</v>
+        <v>69900</v>
       </c>
       <c r="H62" s="3">
-        <v>99900</v>
+        <v>63100</v>
       </c>
       <c r="I62" s="3">
-        <v>120400</v>
+        <v>69500</v>
       </c>
       <c r="J62" s="3">
+        <v>82000</v>
+      </c>
+      <c r="K62" s="3">
         <v>119800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>79000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>88700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>88500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>93100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>103400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>99600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>93300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>94400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>82400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>87300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>79200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>81800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>69900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>72500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>66600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>57400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>73400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>87600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>84500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>83400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>72200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>73800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>61900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>56800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5809,8 +5958,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5910,8 +6062,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6011,109 +6166,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1518700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1509400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1689600</v>
       </c>
-      <c r="F66" s="3">
-        <v>1681200</v>
-      </c>
       <c r="G66" s="3">
-        <v>1703900</v>
+        <v>1681000</v>
       </c>
       <c r="H66" s="3">
-        <v>1751800</v>
+        <v>1703700</v>
       </c>
       <c r="I66" s="3">
-        <v>1767000</v>
+        <v>1751600</v>
       </c>
       <c r="J66" s="3">
+        <v>1766800</v>
+      </c>
+      <c r="K66" s="3">
         <v>1813800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>674400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>401000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>380900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>393300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>403100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>391600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>365300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>383400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>371600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>376500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>361900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>375500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>350400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>366800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>358200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>380200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>391400</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>405500</v>
       </c>
       <c r="AC66" s="3">
         <v>405500</v>
       </c>
       <c r="AD66" s="3">
+        <v>405500</v>
+      </c>
+      <c r="AE66" s="3">
         <v>420800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>406300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>421500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>390100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>406300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>415200</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6149,8 +6310,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6250,8 +6412,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6351,8 +6516,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6452,8 +6620,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6553,109 +6724,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-434800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-427200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-256900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-233800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>408600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>446800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>828800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>858200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>909300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>886500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>834900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>796900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>762100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>727600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>694700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>671200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>655500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>637100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>620900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>611600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>611200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>593600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>588200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>579700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>561600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>549400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>524200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>502300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>503600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>490300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>477700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>467900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6755,8 +6932,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6856,8 +7036,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6957,109 +7140,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-139700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-141400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-313100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-307400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>334300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>366800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>733000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>755900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>792400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>798900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>735000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>737600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>718200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>708400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>704300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>698700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>676400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>677500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>661500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>677000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>688700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>689500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>695200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>682600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>692900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>703300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>693400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>665000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>664700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>639900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>617100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>605300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>585900</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7159,215 +7348,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45592</v>
+      </c>
+      <c r="E80" s="2">
         <v>45501</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45410</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45319</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45228</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45137</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44955</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44864</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44682</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44591</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44409</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44318</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44129</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44038</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43947</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43856</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43765</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43674</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43583</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43492</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43401</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43310</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43219</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43128</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43037</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42946</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42764</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-170300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-642400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-38300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-382000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-29400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-51000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>22700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>51600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>38000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>34800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>34400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>32900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>23500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>15700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>14000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>12700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>19900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>12200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>25200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>13300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>12600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>11800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>8000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7403,109 +7601,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12600</v>
+        <v>9400</v>
       </c>
       <c r="E83" s="3">
-        <v>10500</v>
+        <v>8200</v>
       </c>
       <c r="F83" s="3">
-        <v>8900</v>
+        <v>10400</v>
       </c>
       <c r="G83" s="3">
-        <v>22500</v>
+        <v>7700</v>
       </c>
       <c r="H83" s="3">
-        <v>22000</v>
+        <v>7500</v>
       </c>
       <c r="I83" s="3">
-        <v>24500</v>
+        <v>7400</v>
       </c>
       <c r="J83" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K83" s="3">
         <v>9800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>7300</v>
       </c>
       <c r="L83" s="3">
         <v>7300</v>
       </c>
       <c r="M83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="N83" s="3">
         <v>7700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>9300</v>
-      </c>
-      <c r="W83" s="3">
-        <v>9700</v>
       </c>
       <c r="X83" s="3">
         <v>9700</v>
       </c>
       <c r="Y83" s="3">
+        <v>9700</v>
+      </c>
+      <c r="Z83" s="3">
         <v>10800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>13200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>11800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>11300</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>11600</v>
       </c>
       <c r="AI83" s="3">
         <v>11600</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>11600</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7605,8 +7807,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7706,8 +7911,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7807,8 +8015,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7908,8 +8119,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8009,109 +8223,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-90000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-18800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>77300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>50100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>51000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>66500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>53000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>32600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>27300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>37200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>26100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>45300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>33300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>33400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>47200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>52000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>49300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>35000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>38600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>26900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>35600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>10400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>32900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>39200</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8147,109 +8367,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="L91" s="3">
         <v>-7100</v>
       </c>
-      <c r="E91" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="M91" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="S91" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="T91" s="3">
         <v>-7200</v>
       </c>
-      <c r="I91" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="U91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-10900</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-4900</v>
       </c>
       <c r="AC91" s="3">
         <v>-4900</v>
       </c>
       <c r="AD91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-13800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8349,8 +8573,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8450,109 +8677,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1246600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>20500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-15800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-34100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8588,31 +8821,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8689,8 +8923,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8790,8 +9027,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8891,8 +9131,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8992,129 +9235,135 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>33700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>883100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>248400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-10800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-44200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-37500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-38600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-41400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-34600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-10100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-36100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-15300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-38900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-30300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-32800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-24100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-15800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-47000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-30800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="E101" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I101" s="3">
         <v>-600</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>24</v>
@@ -9134,8 +9383,8 @@
       <c r="O101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -9194,105 +9443,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-24100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-71300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-382300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>255700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>87000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>13900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-19200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>12500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-24400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-24800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>8000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>16800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>13300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>59100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>SMTC</t>
   </si>
@@ -656,469 +656,482 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45683</v>
+      </c>
+      <c r="E7" s="2">
         <v>45592</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45501</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45410</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45319</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45228</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45137</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44955</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44864</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44682</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44591</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44409</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44318</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44129</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44038</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43947</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43856</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43765</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43674</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43583</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43492</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43401</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43310</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43219</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43128</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43037</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42946</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42764</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E8" s="3">
         <v>236800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>215400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>206100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>192900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>238400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>236500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>167500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>177600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>209300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>202100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>190600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>194900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>185000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>170400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>164700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>154100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>143700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>132700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>138000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>141000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>137100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>131400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>160000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>173600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>163200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>130400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>140600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>150300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>153100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>143800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>140000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>137200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E9" s="3">
         <v>113600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>107600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>104200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>99300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>97900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>126700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>122200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>70300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>61900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>74500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>72900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>73400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>71200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>69600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>65500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>64200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>60000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>55400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>51900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>53700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>54800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>52300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>50100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>61100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>67000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>63100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>59000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>55200</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>60900</v>
       </c>
       <c r="AG9" s="3">
         <v>60900</v>
       </c>
       <c r="AH9" s="3">
+        <v>60900</v>
+      </c>
+      <c r="AI9" s="3">
         <v>58900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>56500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>132800</v>
+      </c>
+      <c r="E10" s="3">
         <v>123200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>107700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>101900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>93700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>103000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>111700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>114300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>97200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>115700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>134800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>129200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>117200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>123700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>115400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>104900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>100500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>94100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>88300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>80800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>84300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>86200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>84800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>81300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>98900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>106600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>100100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>71400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>85400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>89400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>92200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>84900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>83500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,112 +1168,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E12" s="3">
         <v>42600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>40100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>41600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>41500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>46900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>47400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>50600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>52500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>35100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>40600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>38800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>38300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>37300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>35500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>36800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>32800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>27900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>29200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>27600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>28000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>27000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>25900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>27200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>27600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>27100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>28100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>26200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>23800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>27600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>27400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>26000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>25400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1363,112 +1380,118 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>146200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>616000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>289500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-18400</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1300</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>30100</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5900</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-25000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1476,7 +1499,7 @@
         <v>2400</v>
       </c>
       <c r="E15" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="F15" s="3">
         <v>2600</v>
@@ -1485,31 +1508,31 @@
         <v>2600</v>
       </c>
       <c r="H15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I15" s="3">
         <v>14900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>15400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>15700</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="L15" s="3">
-        <v>1000</v>
       </c>
       <c r="M15" s="3">
         <v>1000</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
         <v>1000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>1300</v>
       </c>
       <c r="Q15" s="3">
         <v>1300</v>
@@ -1518,52 +1541,52 @@
         <v>1300</v>
       </c>
       <c r="S15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T15" s="3">
         <v>1600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>5100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>6700</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>6500</v>
       </c>
       <c r="AC15" s="3">
         <v>6500</v>
       </c>
       <c r="AD15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="AE15" s="3">
         <v>7000</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>7500</v>
       </c>
       <c r="AF15" s="3">
         <v>7500</v>
       </c>
       <c r="AG15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AH15" s="3">
         <v>6700</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>6300</v>
       </c>
       <c r="AI15" s="3">
         <v>6300</v>
@@ -1571,8 +1594,11 @@
       <c r="AJ15" s="3">
         <v>6300</v>
       </c>
+      <c r="AK15" s="3">
+        <v>6300</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,216 +1632,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>220800</v>
+      </c>
+      <c r="E17" s="3">
         <v>218300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>206000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>195500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>198600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>207400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>249200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>246400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>224700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>147500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>144800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>155100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>148000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>157700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>148800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>142600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>147000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>132900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>126400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>120600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>137700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>123100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>125400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>119200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>126200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>161700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>130300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>133500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>126600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>132700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>134200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>125500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>124700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>98100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E18" s="3">
         <v>18500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-57200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>30100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>64500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>47000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>42600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>37200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>36200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>27800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>33800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>32900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>14000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>17600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>18900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>18300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>15300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>39100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1852,257 +1885,264 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E21" s="3">
         <v>19800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-41800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>38200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>72100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>54800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>49900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>44800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>44200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>35200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>25400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>28800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>24800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>21100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>28300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>26500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>48000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>25800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>45600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>25900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>31500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>30500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>28900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>50000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E22" s="3">
         <v>20800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>23200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>28300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>500</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1200</v>
       </c>
       <c r="Q22" s="3">
         <v>1200</v>
@@ -2111,46 +2151,46 @@
         <v>1200</v>
       </c>
       <c r="S22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T22" s="3">
         <v>1500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2400</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>2200</v>
       </c>
       <c r="AD22" s="3">
         <v>2200</v>
       </c>
       <c r="AE22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AF22" s="3">
         <v>1900</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>2000</v>
       </c>
       <c r="AG22" s="3">
         <v>2000</v>
@@ -2159,221 +2199,230 @@
         <v>2000</v>
       </c>
       <c r="AI22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-166100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-20200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-645700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-38600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-325400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-31800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-60100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>29100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>63300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>46100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>41200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>36100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>35200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>26600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>16200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>19900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>15800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>11000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>16300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>10400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>10700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>33200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>10700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>31300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>10800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>16800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>16700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>15600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>36500</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E24" s="3">
         <v>4000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>56600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-9100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6400</v>
-      </c>
-      <c r="P24" s="3">
-        <v>3000</v>
       </c>
       <c r="Q24" s="3">
         <v>3000</v>
       </c>
       <c r="R24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="S24" s="3">
         <v>3200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-17500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-52200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2476,216 +2525,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-170300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-642400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-38300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-382000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-29400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-51000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>22800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>51300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>38000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>34800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>33100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>32300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>23400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>18300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>16300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>13600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>13200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>26600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>25200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>12400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>63100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>13500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>12600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>11800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-170300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-642400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-38300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-382000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-29400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-51000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>22700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>51600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>38000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>34800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>34400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>32900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>23500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>18500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>16100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>14000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>12700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>26500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>25200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>12400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>63000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>13300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>12600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>11800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2788,8 +2846,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2844,8 +2905,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
@@ -2862,23 +2923,23 @@
       <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>4700</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-64300</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>24</v>
@@ -2892,8 +2953,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2996,8 +3060,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3100,216 +3167,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-170300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-642400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-38300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-382000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-29400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-51000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>22700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>51600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>38000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>34800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>34400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>32900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>23500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>15700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>18500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>16100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>14000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>12700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>19900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>25200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>12400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>13300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>12600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>11800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3412,221 +3488,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-170300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-642400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-38300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-382000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-29400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-51000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>22700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>51600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>38000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>34800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>34400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>32900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>23500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>15700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>18500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>16100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>14000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>12700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>19900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>25200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>12400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>13300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>12600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>11800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45683</v>
+      </c>
+      <c r="E38" s="2">
         <v>45592</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45501</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45410</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45319</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45228</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45137</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44955</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44864</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44682</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44591</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44409</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44318</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44129</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44038</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43947</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43856</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43765</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43674</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43583</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43492</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43401</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43310</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43219</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43128</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43037</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42946</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42764</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3663,8 +3748,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3701,139 +3787,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>151700</v>
+      </c>
+      <c r="E41" s="3">
         <v>136500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>115900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>126800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>128600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>123800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>147900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>164200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>235500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>617800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>362200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>275200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>279600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>276600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>262700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>258200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>268900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>262300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>281500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>268900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>293300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>283100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>287800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>287300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>312100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>312200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>311300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>303300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>307900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>291100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>277900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>281600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>297100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>297900</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>16100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>21500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>22600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>19800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3909,451 +3999,466 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>162500</v>
+      </c>
+      <c r="E43" s="3">
         <v>142500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>153000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>153900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>151600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>156600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>159100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>145400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>161700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>80500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>71100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>66400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>71500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>74300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>73100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>66500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>70400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>58700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>51700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>49500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>61900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>61400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>58600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>66500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>79200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>83800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>78400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>65600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>53200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>66500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>61200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>55900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>51400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E44" s="3">
         <v>163500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>156000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>148500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>189800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>160600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>180200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>213200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>207700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>111100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>107600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>106900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>114000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>105200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>103000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>93900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>87500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>78400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>77500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>76900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>73000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>70100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>75100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>73500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>63700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>61200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>58900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>65500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>71100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>71200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>75000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>76800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>65900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>62700</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E45" s="3">
         <v>91400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>82400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>78200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>98500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>112100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>110200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>117900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>36200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>47000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>40300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>46100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>42700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>47900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>48400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>43200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>37000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>32500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>25400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>31700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>29800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>30300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>29200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>29700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>33000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>29100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>21000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>24800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>21500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>24000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>585500</v>
+      </c>
+      <c r="E46" s="3">
         <v>557800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>541700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>539300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>534200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>572400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>629900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>664400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>722800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>835200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>577100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>495400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>502300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>496400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>484800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>461400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>474700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>447700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>453900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>432300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>460700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>440000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>453300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>457000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>485300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>486400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>478300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>467400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>461200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>449800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>438800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>435700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>438400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>900</v>
+      <c r="D47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E47" s="3">
         <v>900</v>
       </c>
       <c r="F47" s="3">
+        <v>900</v>
+      </c>
+      <c r="G47" s="3">
         <v>10200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>43100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1500</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4420,225 +4525,234 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>24</v>
+      <c r="AH47" s="3">
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AJ47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK47" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>126200</v>
+      </c>
+      <c r="E48" s="3">
         <v>155500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>163000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>169800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>177500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>188100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>192200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>195200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>201100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>153700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>153500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>152700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>154700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>151400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>153700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>146600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>147300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>139600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>142700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>141700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>135400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>134200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>136700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>138200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>118500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>119500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>122600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>122500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>124600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>123400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>118700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>110300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>108900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>95500</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>566200</v>
+      </c>
+      <c r="E49" s="3">
         <v>576600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>575000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>576000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>576800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1181100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1200600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1487600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1496800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>354000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>355000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>356100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>357900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>359000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>360300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>361600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>362900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>364500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>366300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>368300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>371200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>374900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>378600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>382600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>387700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>395500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>393500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>395100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>402100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>409600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>421700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>385200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>391500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>397800</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4741,8 +4855,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4845,112 +4962,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E52" s="3">
         <v>68000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>67900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>66000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>71400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>76800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>83800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>148900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>123900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>114300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>111700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>116000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>114500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>101200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>100100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>97200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>96100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>91100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>81000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>85200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>90100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>87700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>75700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>71300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>83000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>114400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>113800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>97900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>88200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>82100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>76100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>72700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5053,112 +5176,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1419300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1379000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1368000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1376500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1373700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2038100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2118600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2500000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2569600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1466900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1199800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1115900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1130900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1121300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1100000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1069600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1082100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1048000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1054000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1023400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1052400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1039100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1056300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1053400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1062800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1084400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1108800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1098800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1085800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1071000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1061400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1007300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1011500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1001000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5195,8 +5324,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5233,141 +5363,145 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E57" s="3">
         <v>63900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>75800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>64700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>45100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>55000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>52500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>74400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>53800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>48400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>50700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>46400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>52500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>51200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>50200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>47300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>39300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>43300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>48000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>33700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>38900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>40700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>43200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>40600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>37700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>38700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>37200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>39800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>34900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>39300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>42000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E58" s="3">
         <v>6500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>59300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>48700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>43100</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>24</v>
@@ -5384,8 +5518,8 @@
       <c r="Q58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -5403,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
-        <v>18300</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="3">
         <v>18300</v>
@@ -5418,447 +5552,462 @@
         <v>18300</v>
       </c>
       <c r="AC58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="AD58" s="3">
         <v>17300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>16400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>15400</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>14500</v>
       </c>
       <c r="AG58" s="3">
         <v>14500</v>
       </c>
       <c r="AH58" s="3">
-        <v>14400</v>
+        <v>14500</v>
       </c>
       <c r="AI58" s="3">
         <v>14400</v>
       </c>
       <c r="AJ58" s="3">
+        <v>14400</v>
+      </c>
+      <c r="AK58" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="3">
         <v>1400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>57000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>253100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>95000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>86400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>62000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>77700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>77500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>63900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>45300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>59400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>58500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>62800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>48300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>50600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>49100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>53400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>44300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>68500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>61800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>60900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>59400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>73600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>64100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>79100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>51500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>66600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E60" s="3">
         <v>235500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>224700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>224900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>217200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>239000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>321100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>309800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>396900</v>
-      </c>
-      <c r="L60" s="3">
-        <v>140100</v>
       </c>
       <c r="M60" s="3">
         <v>140100</v>
       </c>
       <c r="N60" s="3">
+        <v>140100</v>
+      </c>
+      <c r="O60" s="3">
         <v>110400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>128400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>123900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>116400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>96500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>109600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>105900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>102100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>91600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>98600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>101100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>110600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>103300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>129900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>120600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>115900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>114400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>126200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>118400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>128400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>105300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>123000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>505900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1209700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1213600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1393700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1393100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1397000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1356200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1370300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1297000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>455100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>171900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>181800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>171700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>175600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>175400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>175300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>179200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>183100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>187000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>190800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>194700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>179100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>183700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>188300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>192800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>197400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>202000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>206600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>211100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>215700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>219300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>222900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>226500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>228800</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>87200</v>
+      </c>
+      <c r="E62" s="3">
         <v>73500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>71200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>71000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>69900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>63100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>69500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>82000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>119800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>79000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>88700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>88500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>93100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>103400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>99600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>93300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>94400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>82400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>87300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>79200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>81800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>69900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>72500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>66600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>57400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>73400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>87600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>84500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>83400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>72200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>73800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>61900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>56800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5961,8 +6110,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6065,8 +6217,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6169,112 +6324,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>876900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1518700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1509400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1689600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1681000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1703700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1751600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1766800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1813800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>674400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>401000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>380900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>393300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>403100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>391600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>365300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>383400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>371600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>376500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>361900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>375500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>350400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>366800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>358200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>380200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>391400</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>405500</v>
       </c>
       <c r="AD66" s="3">
         <v>405500</v>
       </c>
       <c r="AE66" s="3">
+        <v>405500</v>
+      </c>
+      <c r="AF66" s="3">
         <v>420800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>406300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>421500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>390100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>406300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>415200</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6311,8 +6472,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6415,8 +6577,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6519,8 +6684,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6623,8 +6791,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6727,112 +6898,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72" s="3">
         <v>-434800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-427200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-256900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-233800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>408600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>446800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>828800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>858200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>909300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>886500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>834900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>796900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>762100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>727600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>694700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>671200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>655500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>637100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>620900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>611600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>611200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>593600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>588200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>579700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>561600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>549400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>524200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>502300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>503600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>490300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>477700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>467900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6935,8 +7112,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7039,8 +7219,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7143,112 +7326,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>542400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-139700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-141400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-313100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-307400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>334300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>366800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>733000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>755900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>792400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>798900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>735000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>737600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>718200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>708400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>704300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>698700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>676400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>677500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>661500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>677000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>688700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>689500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>695200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>682600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>692900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>703300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>693400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>665000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>664700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>639900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>617100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>605300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>585900</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7351,221 +7540,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45683</v>
+      </c>
+      <c r="E80" s="2">
         <v>45592</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45501</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45410</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45319</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45228</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45137</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44955</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44864</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44682</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44591</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44409</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44318</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44129</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44038</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43947</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43856</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43765</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43674</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43583</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43492</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43401</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43310</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43219</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43128</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43037</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42946</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42764</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-170300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-642400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-38300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-382000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-29400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-51000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>22700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>51600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>38000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>34800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>34400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>32900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>23500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>15700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>18500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>16100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>14000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>12700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>19900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>25200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>12400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>13300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>12600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>11800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7602,112 +7800,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E83" s="3">
         <v>9400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>7300</v>
       </c>
       <c r="M83" s="3">
         <v>7300</v>
       </c>
       <c r="N83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="O83" s="3">
         <v>7700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>8500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>9300</v>
-      </c>
-      <c r="X83" s="3">
-        <v>9700</v>
       </c>
       <c r="Y83" s="3">
         <v>9700</v>
       </c>
       <c r="Z83" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AA83" s="3">
         <v>10800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>13200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>12700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>11800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>11300</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>11600</v>
       </c>
       <c r="AJ83" s="3">
         <v>11600</v>
       </c>
+      <c r="AK83" s="3">
+        <v>11600</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7810,8 +8012,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7914,8 +8119,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8018,8 +8226,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8122,8 +8333,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8226,112 +8440,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" s="3">
         <v>29600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-90000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-18800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>77300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>50100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>51000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>66500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>53000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>32600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>27300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>37200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>26100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>45300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>33300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>33400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>47200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>52000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>49300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>35000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>38600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>26900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>35600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>10400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>32900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>39200</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8368,112 +8588,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-15300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-4900</v>
       </c>
       <c r="AD91" s="3">
         <v>-4900</v>
       </c>
       <c r="AE91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-13800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8576,8 +8800,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8680,112 +8907,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1246600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>20500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-15800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-12300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-34100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8822,8 +9055,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8848,8 +9082,8 @@
       <c r="J96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8926,8 +9160,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9030,8 +9267,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9134,8 +9374,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9238,126 +9481,132 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>33700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>883100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>248400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-44200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-37500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-38600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-41400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-34600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-10100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-36100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-15300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-38900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-30300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-32800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-24100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-15800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-47000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-30800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>24</v>
@@ -9386,8 +9635,8 @@
       <c r="P101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -9446,108 +9695,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>20600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-24100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-71300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-382300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>255700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>87000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>13900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-19200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>12500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-24400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>8000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>16800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>13300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>59100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>SMTC</t>
   </si>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>8900</v>
+        <v>7900</v>
       </c>
       <c r="E14" s="3">
         <v>700</v>
@@ -1639,7 +1639,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>220800</v>
+        <v>221800</v>
       </c>
       <c r="E17" s="3">
         <v>218300</v>
@@ -1746,7 +1746,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>30200</v>
+        <v>29200</v>
       </c>
       <c r="E18" s="3">
         <v>18500</v>
@@ -1892,7 +1892,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="E20" s="3">
         <v>1100</v>
@@ -1999,7 +1999,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>33900</v>
+        <v>32900</v>
       </c>
       <c r="E21" s="3">
         <v>19800</v>
@@ -2213,7 +2213,7 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="E23" s="3">
         <v>-3600</v>
@@ -3176,7 +3176,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E32" s="3">
         <v>-1100</v>
@@ -3901,7 +3901,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="E42" s="3">
         <v>16100</v>
@@ -4008,7 +4008,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>162500</v>
+        <v>188100</v>
       </c>
       <c r="E43" s="3">
         <v>142500</v>
@@ -4115,7 +4115,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>163600</v>
+        <v>198400</v>
       </c>
       <c r="E44" s="3">
         <v>163500</v>
@@ -4222,7 +4222,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>94200</v>
+        <v>6300</v>
       </c>
       <c r="E45" s="3">
         <v>91400</v>
@@ -4435,8 +4435,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>24</v>
+      <c r="D47" s="3">
+        <v>39100</v>
       </c>
       <c r="E47" s="3">
         <v>900</v>
@@ -4448,7 +4448,7 @@
         <v>10200</v>
       </c>
       <c r="H47" s="3">
-        <v>43100</v>
+        <v>200</v>
       </c>
       <c r="I47" s="3">
         <v>10700</v>
@@ -4543,7 +4543,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>126200</v>
+        <v>147900</v>
       </c>
       <c r="E48" s="3">
         <v>155500</v>
@@ -4650,7 +4650,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>566200</v>
+        <v>563000</v>
       </c>
       <c r="E49" s="3">
         <v>576600</v>
@@ -4662,7 +4662,7 @@
         <v>576000</v>
       </c>
       <c r="H49" s="3">
-        <v>576800</v>
+        <v>575800</v>
       </c>
       <c r="I49" s="3">
         <v>1181100</v>
@@ -4971,7 +4971,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100300</v>
+        <v>39500</v>
       </c>
       <c r="E52" s="3">
         <v>68000</v>
@@ -4983,7 +4983,7 @@
         <v>66000</v>
       </c>
       <c r="H52" s="3">
-        <v>24200</v>
+        <v>67000</v>
       </c>
       <c r="I52" s="3">
         <v>71400</v>
@@ -5477,7 +5477,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>45600</v>
+        <v>51600</v>
       </c>
       <c r="E58" s="3">
         <v>6500</v>
@@ -5583,8 +5583,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>24</v>
+      <c r="D59" s="3">
+        <v>56100</v>
       </c>
       <c r="E59" s="3">
         <v>1400</v>
@@ -5798,7 +5798,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>505900</v>
+        <v>524400</v>
       </c>
       <c r="E61" s="3">
         <v>1209700</v>
@@ -5905,7 +5905,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>87200</v>
+        <v>68600</v>
       </c>
       <c r="E62" s="3">
         <v>73500</v>
@@ -6333,7 +6333,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>876900</v>
+        <v>876800</v>
       </c>
       <c r="E66" s="3">
         <v>1518700</v>
@@ -6906,8 +6906,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>24</v>
+      <c r="D72" s="3">
+        <v>-395700</v>
       </c>
       <c r="E72" s="3">
         <v>-434800</v>
@@ -8448,8 +8448,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>24</v>
+      <c r="D89" s="3">
+        <v>33500</v>
       </c>
       <c r="E89" s="3">
         <v>29600</v>
@@ -8594,8 +8594,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>24</v>
+      <c r="D91" s="3">
+        <v>-2600</v>
       </c>
       <c r="E91" s="3">
         <v>-500</v>
@@ -8915,8 +8915,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>24</v>
+      <c r="D94" s="3">
+        <v>-7800</v>
       </c>
       <c r="E94" s="3">
         <v>-1400</v>
@@ -9489,8 +9489,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>24</v>
+      <c r="D100" s="3">
+        <v>-9600</v>
       </c>
       <c r="E100" s="3">
         <v>-7500</v>
@@ -9704,7 +9704,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>15200</v>
       </c>
       <c r="E102" s="3">
         <v>20600</v>

--- a/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>SMTC</t>
   </si>
@@ -656,482 +656,494 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45774</v>
+      </c>
+      <c r="E7" s="2">
         <v>45683</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45592</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45501</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45410</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45319</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45228</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45137</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44955</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44864</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44682</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44591</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44409</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44318</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44129</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44038</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43947</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43856</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43765</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43674</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43583</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43492</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43401</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43310</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43219</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43128</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43037</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42946</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42764</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>251100</v>
+      </c>
+      <c r="E8" s="3">
         <v>251000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>236800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>215400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>206100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>192900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>238400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>236500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>167500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>177600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>209300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>202100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>190600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>194900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>185000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>170400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>164700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>154100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>143700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>132700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>138000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>141000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>137100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>131400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>160000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>173600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>163200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>130400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>140600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>150300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>153100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>143800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>140000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>137200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>117600</v>
+      </c>
+      <c r="E9" s="3">
         <v>118200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>113600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>107600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>104200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>99300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>97900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>126700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>122200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>70300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>61900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>74500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>72900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>73400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>71200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>69600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>65500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>64200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>60000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>55400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>51900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>53700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>54800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>52300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>50100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>61100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>67000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>63100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>59000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>55200</v>
-      </c>
-      <c r="AG9" s="3">
-        <v>60900</v>
       </c>
       <c r="AH9" s="3">
         <v>60900</v>
       </c>
       <c r="AI9" s="3">
+        <v>60900</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>58900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>56500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>133500</v>
+      </c>
+      <c r="E10" s="3">
         <v>132800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>123200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>107700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>101900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>93700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>103000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>111700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>114300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>97200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>115700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>134800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>129200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>117200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>123700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>115400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>104900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>100500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>94100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>88300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>80800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>84300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>86200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>84800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>81300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>98900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>106600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>100100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>71400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>85400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>89400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>92200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>84900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>83500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1169,115 +1181,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E12" s="3">
         <v>46700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>42600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>40100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>41600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>41500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>46900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>47400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>50600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>52500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>35100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>40600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>38800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>38300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>37300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>35500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>36800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>32800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>27900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>29200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>27600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>28000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>27000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>25900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>27200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>27600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>27100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>28100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>26200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>23800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>27600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>27400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>25400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1383,115 +1399,121 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3">
         <v>7900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>146200</v>
       </c>
-      <c r="G14" s="3">
-        <v>8600</v>
-      </c>
       <c r="H14" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I14" s="3">
         <v>616000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>289500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-18400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1300</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>2000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>30100</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>5900</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-25000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1502,7 +1524,7 @@
         <v>2400</v>
       </c>
       <c r="F15" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="G15" s="3">
         <v>2600</v>
@@ -1511,31 +1533,31 @@
         <v>2600</v>
       </c>
       <c r="I15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J15" s="3">
         <v>14900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>15400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>15700</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="M15" s="3">
-        <v>1000</v>
       </c>
       <c r="N15" s="3">
         <v>1000</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1300</v>
       </c>
       <c r="R15" s="3">
         <v>1300</v>
@@ -1544,52 +1566,52 @@
         <v>1300</v>
       </c>
       <c r="T15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U15" s="3">
         <v>1600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>5100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>6700</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>6500</v>
       </c>
       <c r="AD15" s="3">
         <v>6500</v>
       </c>
       <c r="AE15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="AF15" s="3">
         <v>7000</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>7500</v>
       </c>
       <c r="AG15" s="3">
         <v>7500</v>
       </c>
       <c r="AH15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AI15" s="3">
         <v>6700</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>6300</v>
       </c>
       <c r="AJ15" s="3">
         <v>6300</v>
@@ -1597,8 +1619,11 @@
       <c r="AK15" s="3">
         <v>6300</v>
       </c>
+      <c r="AL15" s="3">
+        <v>6300</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1633,222 +1658,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>213900</v>
+      </c>
+      <c r="E17" s="3">
         <v>221800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>218300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>206000</v>
       </c>
-      <c r="G17" s="3">
-        <v>195500</v>
-      </c>
       <c r="H17" s="3">
+        <v>200700</v>
+      </c>
+      <c r="I17" s="3">
         <v>198600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>207400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>249200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>246400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>224700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>147500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>144800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>155100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>148000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>157700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>148800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>142600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>147000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>132900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>126400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>120600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>137700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>123100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>125400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>119200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>126200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>161700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>130300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>133500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>126600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>132700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>134200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>125500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>124700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>98100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E18" s="3">
         <v>29200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9300</v>
       </c>
-      <c r="G18" s="3">
-        <v>10600</v>
-      </c>
       <c r="H18" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-5600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-57200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>30100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>64500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>47000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>42600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>37200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>36200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>27800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>21200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>12200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>33800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>32900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>14000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>17600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>18900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>18300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>15300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>39100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1886,266 +1918,273 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E21" s="3">
         <v>32900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>10900</v>
       </c>
-      <c r="G21" s="3">
-        <v>13700</v>
-      </c>
       <c r="H21" s="3">
+        <v>8500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-5000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-41800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>38200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>72100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>54800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>49900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>44800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>44200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>35200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>25400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>28800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>24800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>21100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>28300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>22700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>26500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>48000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>25800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>45600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>25900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>31500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>30500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>28900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>26000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>50000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E22" s="3">
         <v>17500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>28600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>23200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>28300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1200</v>
       </c>
       <c r="R22" s="3">
         <v>1200</v>
@@ -2154,46 +2193,46 @@
         <v>1200</v>
       </c>
       <c r="T22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U22" s="3">
         <v>1500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>4900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2400</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>2200</v>
       </c>
       <c r="AE22" s="3">
         <v>2200</v>
       </c>
       <c r="AF22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AG22" s="3">
         <v>1900</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>2000</v>
       </c>
       <c r="AH22" s="3">
         <v>2000</v>
@@ -2202,227 +2241,236 @@
         <v>2000</v>
       </c>
       <c r="AJ22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AK22" s="3">
         <v>3400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-166100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-20200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-645700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-38600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-325400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-60100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>29100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>63300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>46100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>41200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>35200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>26600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>16200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>19900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>15800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>11000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>16300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>10400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>33200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>31300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>16800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>16700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>15600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>11000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>36500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-33200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>56600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-9100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6400</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>3000</v>
       </c>
       <c r="R24" s="3">
         <v>3000</v>
       </c>
       <c r="S24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="T24" s="3">
         <v>3200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>8400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-17500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-52200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2528,222 +2576,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E26" s="3">
         <v>39100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-170300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-642400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-382000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-29400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-51000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>22800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>51300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>38000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>34800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>33100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>32300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>23400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>15300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>18300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>13600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>13200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>26600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>25200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>12400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>63100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>13500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>12600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>8000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E27" s="3">
         <v>39100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-170300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-642400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-382000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-51000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>51600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>38000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>34800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>34400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>32900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>23500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>14000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>12700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>26500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>25200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>12400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>63000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>13300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>12600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>8000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2849,8 +2906,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +2968,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>24</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>24</v>
@@ -2926,23 +2986,23 @@
       <c r="AA29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>4700</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-64300</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>24</v>
@@ -2956,8 +3016,11 @@
       <c r="AK29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3063,8 +3126,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3170,222 +3236,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E33" s="3">
         <v>39100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-170300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-642400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-382000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-51000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>51600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>38000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>34800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>34400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>32900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>23500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>15700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>9600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>14000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>12700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>19900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>25200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>12400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>13300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>12600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>8000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3491,227 +3566,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E35" s="3">
         <v>39100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-170300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-642400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-382000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-51000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>51600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>38000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>34800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>34400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>32900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>23500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>15700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>9600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>14000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>12700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>19900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>25200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>12400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>13300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>12600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>8000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45774</v>
+      </c>
+      <c r="E38" s="2">
         <v>45683</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45592</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45501</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45410</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45319</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45228</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45137</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44955</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44864</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44682</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44591</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44409</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44318</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44129</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44038</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43947</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43856</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43765</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43674</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43583</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43492</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43401</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43310</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43219</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43128</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43037</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42946</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42764</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3749,8 +3833,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3788,115 +3873,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>156500</v>
+      </c>
+      <c r="E41" s="3">
         <v>151700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>136500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>115900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>126800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>128600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>123800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>147900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>164200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>235500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>617800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>362200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>275200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>279600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>276600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>262700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>258200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>268900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>262300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>281500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>268900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>293300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>283100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>287800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>287300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>312100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>312200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>311300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>303300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>307900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>291100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>277900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>281600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>297100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>297900</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3904,29 +3993,29 @@
         <v>12700</v>
       </c>
       <c r="E42" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F42" s="3">
         <v>16100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>21500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>14500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>22900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>19800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -4002,466 +4091,481 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>165700</v>
+      </c>
+      <c r="E43" s="3">
         <v>188100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>142500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>153000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>153900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>151600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>156600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>159100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>145400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>161700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>80500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>71100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>66400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>71500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>74300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>73100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>66500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>70400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>58700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>51700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>49500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>61900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>61400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>58600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>66500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>79200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>83800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>78400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>65600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>53200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>66500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>61200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>55900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>51400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E44" s="3">
         <v>198400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>163500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>156000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>148500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>189800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>160600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>180200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>213200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>207700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>111100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>107600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>106900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>114000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>105200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>103000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>93900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>87500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>78400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>77500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>76900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>73000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>70100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>75100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>73500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>63700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>61200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>58900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>65500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>71100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>71200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>75000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>76800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>65900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>62700</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>83800</v>
+      </c>
+      <c r="E45" s="3">
         <v>6300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>91400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>82400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>78200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>98500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>112100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>110200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>117900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>36200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>47000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>37200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>40300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>46100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>42700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>47900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>48400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>43200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>37000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>32500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>25400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>31700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>29800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>30300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>29200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>29700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>33000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>29100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>21000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>24800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>21500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>24000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>598000</v>
+      </c>
+      <c r="E46" s="3">
         <v>585500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>557800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>541700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>539300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>534200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>572400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>629900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>664400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>722800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>835200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>577100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>495400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>502300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>496400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>484800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>461400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>474700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>447700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>453900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>432300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>460700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>440000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>453300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>457000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>485300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>486400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>478300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>467400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>461200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>449800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>438800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>435700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>438400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="3">
         <v>39100</v>
-      </c>
-      <c r="E47" s="3">
-        <v>900</v>
       </c>
       <c r="F47" s="3">
         <v>900</v>
       </c>
       <c r="G47" s="3">
+        <v>900</v>
+      </c>
+      <c r="H47" s="3">
         <v>10200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1500</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4528,231 +4632,240 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>24</v>
+      <c r="AI47" s="3">
+        <v>0</v>
       </c>
       <c r="AJ47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL47" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>143200</v>
+      </c>
+      <c r="E48" s="3">
         <v>147900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>155500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>163000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>169800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>177500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>188100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>192200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>195200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>201100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>153700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>153500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>152700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>154700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>151400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>153700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>146600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>147300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>139600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>142700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>141700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>135400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>134200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>136700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>138200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>118500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>119500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>122600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>122500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>124600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>123400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>118700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>110300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>108900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>95500</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>566500</v>
+      </c>
+      <c r="E49" s="3">
         <v>563000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>576600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>575000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>576000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>575800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1181100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1200600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1487600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1496800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>354000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>355000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>356100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>357900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>359000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>360300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>361600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>362900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>364500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>366300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>368300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>371200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>374900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>378600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>382600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>387700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>395500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>393500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>395100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>402100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>409600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>421700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>385200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>391500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>397800</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4858,8 +4971,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4965,115 +5081,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>81800</v>
+      </c>
+      <c r="E52" s="3">
         <v>39500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>68000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>67900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>66000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>67000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>71400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>76800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>83800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>148900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>123900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>114300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>111700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>116000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>114500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>101200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>100100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>97200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>96100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>91100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>81000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>85200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>90100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>87700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>75700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>71300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>83000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>114400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>113800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>97900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>88200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>82100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>76100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>72700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5179,115 +5301,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1432000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1419300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1379000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1368000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1376500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1373700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2038100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2118600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2500000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2569600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1466900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1199800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1115900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1130900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1121300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1100000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1069600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1082100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1048000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1054000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1023400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1052400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1039100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1056300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1053400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1062800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1084400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1108800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1098800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1085800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1071000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1061400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1007300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1011500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1001000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5325,8 +5453,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5364,147 +5493,151 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E57" s="3">
         <v>59200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>63900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>75800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>64700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>45100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>55000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>52500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>74400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>53800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>48400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>50700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>46400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>52500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>51200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>50200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>47300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>39300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>43300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>48000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>33700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>38900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>40700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>43200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>40600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>37700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>38700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>37200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>39800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>34900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>39300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>42000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E58" s="3">
         <v>51600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>59300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>48700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>43100</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>24</v>
@@ -5521,8 +5654,8 @@
       <c r="R58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5540,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
-        <v>18300</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="3">
         <v>18300</v>
@@ -5555,459 +5688,474 @@
         <v>18300</v>
       </c>
       <c r="AD58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="AE58" s="3">
         <v>17300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>16400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>15400</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>14500</v>
       </c>
       <c r="AH58" s="3">
         <v>14500</v>
       </c>
       <c r="AI58" s="3">
-        <v>14400</v>
+        <v>14500</v>
       </c>
       <c r="AJ58" s="3">
         <v>14400</v>
       </c>
       <c r="AK58" s="3">
+        <v>14400</v>
+      </c>
+      <c r="AL58" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
         <v>56100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>57000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>253100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>95000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>86400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>62000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>77700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>77500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>63900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>45300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>59400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>58500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>62800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>48300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>50600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>49100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>53400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>44300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>68500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>61800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>60900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>59400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>73600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>64100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>79100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>51500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>66600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E60" s="3">
         <v>283000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>235500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>224700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>224900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>217200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>239000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>321100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>309800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>396900</v>
-      </c>
-      <c r="M60" s="3">
-        <v>140100</v>
       </c>
       <c r="N60" s="3">
         <v>140100</v>
       </c>
       <c r="O60" s="3">
+        <v>140100</v>
+      </c>
+      <c r="P60" s="3">
         <v>110400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>128400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>123900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>116400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>96500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>109600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>105900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>102100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>91600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>98600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>101100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>110600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>103300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>129900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>120600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>115900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>114400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>126200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>118400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>128400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>105300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>123000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>562500</v>
+      </c>
+      <c r="E61" s="3">
         <v>524400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1209700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1213600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1393700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1393100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1397000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1356200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1370300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1297000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>455100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>171900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>181800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>171700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>175600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>175400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>175300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>179200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>183100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>187000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>190800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>194700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>179100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>183700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>188300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>192800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>197400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>202000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>206600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>211100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>215700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>219300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>222900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>226500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>228800</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E62" s="3">
         <v>68600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>73500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>71200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>71000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>69900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>63100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>69500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>82000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>119800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>79000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>88700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>88500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>93100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>103400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>99600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>93300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>94400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>82400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>87300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>79200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>81800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>69900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>72500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>66600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>57400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>73400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>87600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>84500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>83400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>72200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>73800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>61900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>56800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6113,8 +6261,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6220,8 +6371,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6327,115 +6481,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>863100</v>
+      </c>
+      <c r="E66" s="3">
         <v>876800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1518700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1509400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1689600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1681000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1703700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1751600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1766800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1813800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>674400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>401000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>380900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>393300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>403100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>391600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>365300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>383400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>371600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>376500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>361900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>375500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>350400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>366800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>358200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>380200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>391400</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>405500</v>
       </c>
       <c r="AE66" s="3">
         <v>405500</v>
       </c>
       <c r="AF66" s="3">
+        <v>405500</v>
+      </c>
+      <c r="AG66" s="3">
         <v>420800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>406300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>421500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>390100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>406300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>415200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6473,8 +6633,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6580,8 +6741,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6687,8 +6851,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6794,8 +6961,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6901,115 +7071,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-376300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-395700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-434800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-427200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-256900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-233800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>408600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>446800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>828800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>858200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>909300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>886500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>834900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>796900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>762100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>727600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>694700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>671200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>655500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>637100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>620900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>611600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>611200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>593600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>588200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>579700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>561600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>549400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>524200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>502300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>503600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>490300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>477700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>467900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7115,8 +7291,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7222,8 +7401,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7329,115 +7511,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>568800</v>
+      </c>
+      <c r="E76" s="3">
         <v>542400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-139700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-141400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-313100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-307400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>334300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>366800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>733000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>755900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>792400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>798900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>735000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>737600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>718200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>708400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>704300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>698700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>676400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>677500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>661500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>677000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>688700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>689500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>695200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>682600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>692900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>703300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>693400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>665000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>664700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>639900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>617100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>605300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>585900</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7543,227 +7731,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45774</v>
+      </c>
+      <c r="E80" s="2">
         <v>45683</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45592</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45501</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45410</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45319</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45228</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45137</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44955</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44864</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44682</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44591</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44409</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44318</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44129</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44038</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43947</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43856</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43765</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43674</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43583</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43492</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43401</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43310</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43219</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43128</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43037</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42946</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42764</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E81" s="3">
         <v>39100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-170300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-642400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-382000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-51000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>51600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>38000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>34800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>34400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>32900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>23500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>15700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>9600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>14000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>12700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>19900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>25200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>12400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>13300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>12600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>8000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7801,115 +7998,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E83" s="3">
         <v>7800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>7300</v>
       </c>
       <c r="N83" s="3">
         <v>7300</v>
       </c>
       <c r="O83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="P83" s="3">
         <v>7700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>9300</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>9700</v>
       </c>
       <c r="Z83" s="3">
         <v>9700</v>
       </c>
       <c r="AA83" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AB83" s="3">
         <v>10800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>13200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>12700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>11800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>11300</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>11600</v>
       </c>
       <c r="AK83" s="3">
         <v>11600</v>
       </c>
+      <c r="AL83" s="3">
+        <v>11600</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8015,8 +8216,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8122,8 +8326,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8229,8 +8436,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8336,8 +8546,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8443,115 +8656,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E89" s="3">
         <v>33500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>29600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-90000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-18800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>77300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>50100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>51000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>66500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>53000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>32600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>27300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>37200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>26100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>45300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>33300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>33400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>47200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>52000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>49300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>35000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>38600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>26900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>35600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>32900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>39200</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8589,115 +8808,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-15300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-4900</v>
       </c>
       <c r="AE91" s="3">
         <v>-4900</v>
       </c>
       <c r="AF91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-13800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8803,8 +9026,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8910,115 +9136,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1246600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>20500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-15800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-12300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-34100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9056,8 +9288,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9085,8 +9318,8 @@
       <c r="K96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9163,8 +9396,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9270,8 +9506,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9377,8 +9616,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9484,132 +9726,138 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>33700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>883100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>248400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-44200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-38600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-41400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-34600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-10100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-36100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-15300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-38900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-30300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-32800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-24100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-15800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-47000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-30800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>24</v>
@@ -9638,8 +9886,8 @@
       <c r="Q101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -9698,111 +9946,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E102" s="3">
         <v>15200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-24100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-71300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-382300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>255700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>87000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>13900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-19200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>12500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-24400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>10300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>8000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>16800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>13300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>59100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
@@ -4170,7 +4170,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -4518,7 +4518,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>93900</v>
+        <v>84400</v>
       </c>
       <c r="E45" s="3">
         <v>97100</v>
@@ -5994,7 +5994,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E59" s="3">
         <v>500</v>

--- a/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>SMTC</t>
   </si>
@@ -656,520 +656,545 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46138</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46047</v>
+      </c>
+      <c r="F7" s="2">
         <v>45956</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45865</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45774</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45683</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45592</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45501</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45410</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45319</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45228</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45137</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45046</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44955</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44864</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44773</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44682</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44591</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44500</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44409</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44318</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44227</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44129</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44038</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43947</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43856</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43765</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43674</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43583</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43492</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43401</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43310</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43219</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43128</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43037</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42946</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42855</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42764</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>291000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>274400</v>
+      </c>
+      <c r="F8" s="3">
         <v>267000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>257600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>251100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>251000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>236800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>215400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>206100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>192900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>200900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>238400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>236500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>167500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>177600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>209300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>202100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>190600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>194900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>185000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>170400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>164700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>154100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>143700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>132700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>138000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>141000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>137100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>131400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>160000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>173600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>163200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>130400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>140600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>150300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>153100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>143800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>140000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>137200</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>137800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>133500</v>
+      </c>
+      <c r="F9" s="3">
         <v>126300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>121300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>117600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>118200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>113600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>107600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>104200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>99300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>97900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>126700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>122200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>70300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>61900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>74500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>72900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>73400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>71200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>69600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>65500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>64200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>60000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>55400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>51900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>53700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>54800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>52300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>50100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>61100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>67000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>63100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>59000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>55200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>60900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>60900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>58900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>56500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>153200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>140800</v>
+      </c>
+      <c r="F10" s="3">
         <v>140700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>136300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>133500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>132800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>123200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>107700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>101900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>93700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>103000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>111700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>114300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>97200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>115700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>134800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>129200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>117200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>123700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>115400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>104900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>100500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>94100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>88300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>80800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>84300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>86200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>84800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>81300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>98900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>106600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>100100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>71400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>85400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>89400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>92200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>84900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>83500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1210,124 +1235,132 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>51200</v>
+      </c>
+      <c r="F12" s="3">
         <v>49400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>48200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>47500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>46700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>42600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>40100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>41600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>41500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>46900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>47400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>50600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>52500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>35100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>40600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>38800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>38300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>37300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>35500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>36800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>32800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>27900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>29200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>27600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>28000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>27000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>25900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>27200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>27600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>27100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>28100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>26200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>23800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>27600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>27400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>26000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>25400</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1442,132 +1475,144 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>55700</v>
+      </c>
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>43500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>1200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>7900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>146200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>3400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>616000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>7900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>289500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>2100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>11100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>9300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-18400</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>400</v>
-      </c>
-      <c r="T14" s="3">
-        <v>200</v>
-      </c>
-      <c r="U14" s="3">
-        <v>500</v>
       </c>
       <c r="V14" s="3">
         <v>200</v>
       </c>
       <c r="W14" s="3">
+        <v>500</v>
+      </c>
+      <c r="X14" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>1500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>3600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>1300</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>2000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>30100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>800</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>1800</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AP14" s="3">
         <v>-25000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="E15" s="3">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="F15" s="3">
         <v>2400</v>
@@ -1579,103 +1624,109 @@
         <v>2400</v>
       </c>
       <c r="I15" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="J15" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="K15" s="3">
         <v>2600</v>
       </c>
       <c r="L15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N15" s="3">
         <v>14900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>15400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>15700</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
       </c>
       <c r="S15" s="3">
         <v>1000</v>
       </c>
       <c r="T15" s="3">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="U15" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="V15" s="3">
         <v>1300</v>
       </c>
       <c r="W15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Y15" s="3">
         <v>1600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>1800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>2000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>2800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>3700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>3800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>3900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>5100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>6700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>6500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>6500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>7000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>7500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>6700</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>6300</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>6300</v>
       </c>
       <c r="AN15" s="3">
         <v>6300</v>
       </c>
+      <c r="AO15" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>6300</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1713,240 +1764,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>264100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>247300</v>
+      </c>
+      <c r="F17" s="3">
         <v>235200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>230300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>213900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>221800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>218300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>206000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>200700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>198600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>207400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>249200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>246400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>224700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>147500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>144800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>155100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>148000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>157700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>148800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>142600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>147000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>132900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>126400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>120600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>137700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>123100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>125400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>119200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>126200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>161700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>130300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>133500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>126600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>132700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>134200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>125500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>124700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>98100</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>27000</v>
+      </c>
+      <c r="F18" s="3">
         <v>31800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>27300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>37200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>29200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>18500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>9300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>5400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-5600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-6500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-10800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-9800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-57200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>30100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>64500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>47000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>42600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>37200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>36200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>27800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>17700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>21200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>17300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>12100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>17900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>11700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>12200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>33800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>11900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>32900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>17600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>18900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>18300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>15300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>39100</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1987,588 +2052,620 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-3500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>5500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-900</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
-        <v>200</v>
+        <v>-900</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
       <c r="W20" s="3">
+        <v>200</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>400</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>1300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>3500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>1900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>1300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>-600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>28700</v>
+      </c>
+      <c r="F21" s="3">
         <v>33800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>28300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>37800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>32900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>19800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>10900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>8500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-5000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>11900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>3100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>5400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-41800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>38200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>72100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>54800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>49900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>44800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>44200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>35200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>25400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>28800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>24800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>21100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>9600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>28300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>22700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>26500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>48000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>25800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>45600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>9500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>25900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>31500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>30500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>28900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>26000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>50000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F22" s="3">
         <v>27000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>5200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>6600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>17500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>20800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>28600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>23200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>22800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>28300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>24200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>20500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>8400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>1800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>1000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>500</v>
-      </c>
-      <c r="T22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1200</v>
       </c>
       <c r="V22" s="3">
         <v>1200</v>
       </c>
       <c r="W22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y22" s="3">
         <v>1500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>1000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>1300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>1600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>1900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>2200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>2600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>4900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>2500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>2400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>2200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>2200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>1900</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>2000</v>
       </c>
       <c r="AL22" s="3">
         <v>2000</v>
       </c>
       <c r="AM22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AN22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AO22" s="3">
         <v>3400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="F23" s="3">
         <v>4500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-22300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>28000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>6000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-166100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-20200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-645700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-38600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-325400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-31800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-60100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>29100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>63300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>46100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>41200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>36100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>35200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>26600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>16200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>19900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>15800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>11000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>16300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>10400</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>10700</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>33200</v>
       </c>
       <c r="AF23" s="3">
         <v>10700</v>
       </c>
       <c r="AG23" s="3">
+        <v>33200</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>10700</v>
+      </c>
+      <c r="AI23" s="3">
         <v>31300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>16800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>16700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>15600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>11000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>36500</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F24" s="3">
         <v>7300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>4800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>8700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-33200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>4200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>3000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-3300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>56600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-2400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-9100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>6300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>12000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>8100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>6400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>3000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>3000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>3200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>1400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>2800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>2700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>8400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>6600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>3200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>6100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>-17500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-52200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>3300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>4100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>3800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>3000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2683,240 +2780,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-27100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>19300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>39100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-170300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-23200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-642400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-38300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-382000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-29400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-51000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>22800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>51300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>38000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>34800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>33100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>32300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>23400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>15300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>18300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>16300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>9600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>13600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>2000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>13200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>26600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>7400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>25200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>12400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>63100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>13500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>12600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>11800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>8000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-27100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>19300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>39100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-7600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-170300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-23200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-642400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-38300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-382000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-29400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-51000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>22700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>51600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>38000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>34800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>34400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>32900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>23500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>15700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>18500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>16100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>9600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>14000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>2200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>12700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>26500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>7500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>25200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>12400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>63000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>13300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>12600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>11800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>8000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3031,8 +3146,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3099,11 +3220,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>24</v>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>24</v>
@@ -3117,26 +3238,26 @@
       <c r="AD29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>4700</v>
       </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI29" s="3">
-        <v>-64300</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>24</v>
+      <c r="AK29" s="3">
+        <v>-64300</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>24</v>
@@ -3147,8 +3268,14 @@
       <c r="AN29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3263,8 +3390,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3379,240 +3512,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>3500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-5500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>900</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
-        <v>-200</v>
+        <v>900</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
       <c r="W32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-400</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-27100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>19300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>39100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-7600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-170300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-23200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-642400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-38300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-382000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-29400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-51000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>22700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>51600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>38000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>34800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>34400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>32900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>23500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>15700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>18500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>16100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>9600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>14000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>2200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>12700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>19900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>12200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>25200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>12400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>13300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>12600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>11800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>8000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3727,245 +3878,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-27100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>19300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>39100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-7600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-170300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-23200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-642400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-38300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-382000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-29400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-51000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>22700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>51600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>38000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>34800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>34400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>32900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>23500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>15700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>18500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>16100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>9600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>14000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>2200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>12700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>19900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>12200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>25200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>12400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>13300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>12600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>11800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>8000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46138</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46047</v>
+      </c>
+      <c r="F38" s="2">
         <v>45956</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45865</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45774</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45683</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45592</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45501</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45410</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45319</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45228</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45137</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45046</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44955</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44864</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44773</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44682</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44591</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44500</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44409</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44318</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44227</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44129</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44038</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43947</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43856</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43765</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43674</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43583</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43492</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43401</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43310</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43219</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43128</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43037</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42946</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42855</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42764</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4006,8 +4175,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4048,166 +4219,174 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>163300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>195200</v>
+      </c>
+      <c r="F41" s="3">
         <v>164700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>168600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>156500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>151700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>136500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>115900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>126800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>128600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>123800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>147900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>164200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>235500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>617800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>362200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>275200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>279600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>276600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>262700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>258200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>268900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>262300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>281500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>268900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>293300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>283100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>287800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>287300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>312100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>312200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>311300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>303300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>307900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>291100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>277900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>281600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>297100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>297900</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>9500</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>12700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>12700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>16100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>19100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>21500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>14500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>22600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>22900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>19800</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4280,514 +4459,544 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>174800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>196200</v>
+      </c>
+      <c r="F43" s="3">
         <v>164800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>153500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>165700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>188100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>142500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>153000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>153900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>151600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>156600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>159100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>145400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>161700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>80500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>71100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>66400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>71500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>74300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>73100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>66500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>70400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>58700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>51700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>49500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>61900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>61400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>58600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>66500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>79200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>83800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>78400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>65600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>53200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>66500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>61200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>55900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>51400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>204700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>225600</v>
+      </c>
+      <c r="F44" s="3">
         <v>185700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>183300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>170200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>198400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>163500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>156000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>148500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>189800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>160600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>180200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>213200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>207700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>111100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>107600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>106900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>114000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>105200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>103000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>93900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>87500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>78400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>77500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>76900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>73000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>70100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>75100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>73500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>63700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>61200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>58900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>65500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>71100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>71200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>75000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>76800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>65900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>62700</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>83500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F45" s="3">
         <v>84400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>97100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>83800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>6300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>91400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>82400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>78200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>12700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>98500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>112100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>110200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>117900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>25800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>36200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>47000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>37200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>40300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>46100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>42700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>47900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>48400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>43200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>37000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>32500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>25400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>31700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>29800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>30300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>29200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>29700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>33000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>29100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>21000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>24800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>21500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>24000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>648700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>655100</v>
+      </c>
+      <c r="F46" s="3">
         <v>620900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>614900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>598000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>585500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>557800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>541700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>539300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>534200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>572400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>629900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>664400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>722800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>835200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>577100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>495400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>502300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>496400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>484800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>461400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>474700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>447700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>453900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>432300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>460700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>440000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>453300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>457000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>485300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>486400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>478300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>467400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>461200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>449800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>438800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>435700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>438400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>24</v>
+      <c r="E47" s="3">
+        <v>37000</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="3">
         <v>39100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>10200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>10700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>4700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1500</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4851,249 +5060,267 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
-      <c r="AL47" s="3" t="s">
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AM47" s="3" t="s">
+      <c r="AO47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>132800</v>
+      </c>
+      <c r="F48" s="3">
         <v>133100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>139000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>143200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>147900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>155500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>163000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>169800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>177500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>188100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>192200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>195200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>201100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>153700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>153500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>152700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>154700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>151400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>153700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>146600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>147300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>139600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>142700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>141700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>135400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>134200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>136700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>138200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>118500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>119500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>122600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>122500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>124600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>123400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>118700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>110300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>108900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>95500</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>526000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>494400</v>
+      </c>
+      <c r="F49" s="3">
         <v>520300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>522500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>566500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>563000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>576600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>575000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>576000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>575800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1181100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1200600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1487600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1496800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>354000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>355000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>356100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>357900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>359000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>360300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>361600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>362900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>364500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>366300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>368300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>371200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>374900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>378600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>382600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>387700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>395500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>393500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>395100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>402100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>409600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>421700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>385200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>391500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>397800</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5208,8 +5435,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5324,124 +5557,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>53300</v>
+      </c>
+      <c r="F52" s="3">
         <v>92800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>88600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>81800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>39500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>68000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>67900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>66000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>67000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>71400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>76800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>83800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>148900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>123900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>114300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>111700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>116000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>114500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>101200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>100100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>97200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>96100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>91100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>81000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>85200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>90100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>87700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>75700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>71300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>83000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>114400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>113800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>97900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>88200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>82100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>76100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>72700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5556,124 +5801,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1438900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1410300</v>
+      </c>
+      <c r="F54" s="3">
         <v>1405900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1405900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1432000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1419300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1379000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1368000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1376500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1373700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2038100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2118600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2500000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2569600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1466900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1199800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1115900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1130900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1121300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1100000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1069600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1082100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1048000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1054000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1023400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1052400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1039100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1056300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1053400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1062800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1084400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1108800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1098800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>1085800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>1071000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>1061400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>1007300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>1011500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>1001000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5714,8 +5971,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5756,168 +6015,176 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>84100</v>
+      </c>
+      <c r="F57" s="3">
         <v>75200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>70900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>69100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>59200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>63900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>75800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>64700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>45100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>55000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>52500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>74400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>100700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>45100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>53800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>48400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>50700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>46400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>52500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>51200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>50200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>47300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>39300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>43300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>48000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>33700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>38900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>40700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>43200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>40600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>37700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>38700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>37200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>39800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>34900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>39300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>42000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F58" s="3">
         <v>6500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>6600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>6400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>51600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>6500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>6600</v>
-      </c>
-      <c r="J58" s="3">
-        <v>6300</v>
       </c>
       <c r="K58" s="3">
         <v>6600</v>
       </c>
       <c r="L58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M58" s="3">
+        <v>6600</v>
+      </c>
+      <c r="N58" s="3">
         <v>6200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>59300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>48700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>43100</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>24</v>
@@ -5931,11 +6198,11 @@
       <c r="U58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -5950,10 +6217,10 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>18300</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
-        <v>18300</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>18300</v>
@@ -5965,495 +6232,525 @@
         <v>18300</v>
       </c>
       <c r="AG58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="AI58" s="3">
         <v>17300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>16400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>15400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>14500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>14500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>14400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>14400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>61600</v>
+      </c>
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
-        <v>56100</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>55300</v>
+      </c>
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>6300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>57000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>6200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>8800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>253100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>95000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>86400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>62000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>77700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>77500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>63900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>45300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>59400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>58500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>62800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>48300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>50600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>49100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>53400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>44300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>68500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>61800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>60900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>59400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>73600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>64100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>79100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>51500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>66600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>273700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>275900</v>
+      </c>
+      <c r="F60" s="3">
         <v>255100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>243100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>236000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>283000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>235500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>224700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>224900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>217200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>239000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>321100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>309800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>396900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>140100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>140100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>110400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>128400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>123900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>116400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>96500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>109600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>105900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>102100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>91600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>98600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>101100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>110600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>103300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>129900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>120600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>115900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>114400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>126200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>118400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>128400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>105300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>123000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>511500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>511900</v>
+      </c>
+      <c r="F61" s="3">
         <v>509300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>539300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>562500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>524400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1209700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1213600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1393700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1393100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1397000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1356200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1370300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1297000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>455100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>171900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>181800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>171700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>175600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>175400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>175300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>179200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>183100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>187000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>190800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>194700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>179100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>183700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>188300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>192800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>197400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>202000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>206600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>211100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>215700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>219300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>222900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>226500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>228800</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>72700</v>
+      </c>
+      <c r="F62" s="3">
         <v>75200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>69500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>64000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>68600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>73500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>71200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>71000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>69900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>63100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>69500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>82000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>119800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>79000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>88700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>88500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>93100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>103400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>99600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>93300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>94400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>82400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>87300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>79200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>81800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>69900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>72500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>66600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>57400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>73400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>87600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>84500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>83400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>72200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>73800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>61900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>56800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6568,8 +6865,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6684,8 +6987,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6800,124 +7109,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>865600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>860600</v>
+      </c>
+      <c r="F66" s="3">
         <v>840200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>853000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>863100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>876800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1518700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1509400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1689600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1681000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1703700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1751600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1766800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1813800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>674400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>401000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>380900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>393300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>403100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>391600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>365300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>383400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>371600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>376500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>361900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>375500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>350400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>366800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>358200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>380200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>391400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>405500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>405500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>420800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>406300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>421500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>390100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>406300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>415200</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6958,8 +7279,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7074,8 +7397,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7190,8 +7519,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7306,8 +7641,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7422,124 +7763,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-409500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-436100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-406300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-403400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-376300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-395700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-434800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-427200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-256900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-233800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>408600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>446800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>828800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>858200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>909300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>886500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>834900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>796900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>762100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>727600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>694700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>671200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>655500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>637100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>620900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>611600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>611200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>593600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>588200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>579700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>561600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>549400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>524200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>502300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>503600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>490300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>477700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>467900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7654,8 +8007,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7770,8 +8129,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7886,124 +8251,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>573300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>549700</v>
+      </c>
+      <c r="F76" s="3">
         <v>565700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>552900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>568800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>542400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-139700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-141400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-313100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-307400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>334300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>366800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>733000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>755900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>792400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>798900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>735000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>737600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>718200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>708400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>704300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>698700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>676400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>677500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>661500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>677000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>688700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>689500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>695200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>682600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>692900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>703300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>693400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>665000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>664700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>639900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>617100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>605300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>585900</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8118,245 +8495,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46138</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46047</v>
+      </c>
+      <c r="F80" s="2">
         <v>45956</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45865</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45774</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45683</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45592</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45501</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45410</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45319</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45228</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45137</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45046</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44955</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44864</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44773</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44682</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44591</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44500</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44409</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44318</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44227</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44129</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44038</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43947</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43856</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43765</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43674</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43583</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43492</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43401</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43310</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43219</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43128</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43037</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42946</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42855</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42764</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-27100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>19300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>39100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-7600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-170300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-23200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-642400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-38300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-382000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-29400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-51000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>22700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>51600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>38000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>34800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>34400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>32900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>23500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>15700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>18500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>16100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>9600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>14000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>2200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>12700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>19900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>12200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>25200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>12400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>13300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>12600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>11800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>8000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8397,8 +8792,10 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8406,115 +8803,121 @@
         <v>9000</v>
       </c>
       <c r="E83" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F83" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G83" s="3">
         <v>11700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>9300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>7800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>9400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>8200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>10400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>7700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>7500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>7400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>7800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>9800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>7300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>7300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>7700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>8200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>7500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>7800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>7400</v>
-      </c>
-      <c r="W83" s="3">
-        <v>7700</v>
-      </c>
-      <c r="X83" s="3">
-        <v>7900</v>
       </c>
       <c r="Y83" s="3">
         <v>7700</v>
       </c>
       <c r="Z83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AB83" s="3">
         <v>8500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>9300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>9700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>9700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>10800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>12300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>12800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>12100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>12500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>13200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>12700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>11800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>11300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>11600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8629,8 +9032,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8745,8 +9154,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8861,8 +9276,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8977,8 +9398,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9093,124 +9520,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>61500</v>
+      </c>
+      <c r="F89" s="3">
         <v>47500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>44400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>27800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>33500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>29600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>13900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-5800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-12000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-90000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-18800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>18200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>77300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>50100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>51000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>66500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>53000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>32600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>27300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>28400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>37200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>26100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>45300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>33300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>33400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>6700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>47200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>52000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>49300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>35000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>38600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>26900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>35600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>10400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>32900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>39200</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9251,124 +9690,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-2900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-6600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-6900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-14000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-5700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-7300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-8300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-8100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-5300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-7000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-5800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-10900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-15300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-13800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9483,8 +9930,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9599,124 +10052,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-42500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-5100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-5100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-7800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>1800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>3600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-6700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-5200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-14400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1246600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>20500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-10300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-10500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-14000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-7200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-8700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-10500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-15800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-12300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-34100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9757,8 +10222,10 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9795,11 +10262,11 @@
       <c r="N96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9873,8 +10340,14 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9989,8 +10462,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10105,8 +10584,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10221,153 +10706,165 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-47100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-27700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-19400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-9600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-7500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-3200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-13800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-10400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>33700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>883100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>248400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-10800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-44200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-37500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-38600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-41400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-34600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-10100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-38900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-30300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-32800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-24100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-15800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-47000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-30800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>24</v>
@@ -10393,11 +10890,11 @@
       <c r="T101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -10453,120 +10950,132 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>30500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>12100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>15200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>20600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-10800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>4800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-24100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-16300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-71300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-382300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>255700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>87000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-4400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>3000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>13900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>4400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-10700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>6600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-19200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>12500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>10300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>8000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>16800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>13300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>59100</v>
       </c>
     </row>
